--- a/money.xlsx
+++ b/money.xlsx
@@ -1492,47 +1492,47 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>远程工作</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>一直想做的远程工作集合网站，上线了</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>岗位职责：
 前段时间找远程工作，横跳在各个平台之间，
@@ -1545,64 +1545,64 @@
 翻译成了中文</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="K3" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L3" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1201311#reply13</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>远程岗位</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>后端开发</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>远程岗位：高级产品经理（AI 方向），广告接入技术支持工程师，远程 QA 测试工程师， PHP ， web， Flutter</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t>岗位职责：
 1. 负责 AI 相关产品的规划、设计与迭代。
@@ -1624,64 +1624,64 @@
 * 技术壁垒： 通过沉淀针对各主流 CMS 的自动化接入方案，构建联盟在技术服务侧的竞争护城河。</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t>50k+</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t>Telegram: Skyewen20251</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1201527#reply1</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>外企招</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>后端开发</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>外企招聘数据工程师 20-50w/year (接受后端转)-full remote</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>岗位职责：
 这是我之前发的招聘：
@@ -1694,17 +1694,17 @@
 公司简介，福利等见我之前的帖子，总体来说都还挺不错的。</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L5" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1198745#reply4</t>
         </is>

--- a/money.xlsx
+++ b/money.xlsx
@@ -1401,7 +1401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col width="23.5576923076923" customWidth="1" style="1" min="1" max="1"/>
@@ -1492,47 +1492,319 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B3" s="0" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C3" s="0" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>市场营销</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>广告接入技术支持工程师
+30k 在家 办公</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>岗位职责：
+1.  深度支持接入： 指导站长在 WP (Hooks/Footer/Plugin)、AppleCMS 、Z-Blog 等各类复杂 CMS 环境下完成广告代码的**高性能植入**。
+2.  技术故障攻坚： 独立定位并排查 JS 报错、CSS 布局塌陷、Iframe 权限限制**及 **CDN 缓存同步**等接入难题。
+3.  **环境适配优化： 针对不同浏览器内核及广告拦截器（ AdBlocker ），提供**代码混淆、动态注入或域名反代**等技术绕过与兼容性建议。  Ym9iY3J0Z3ZzQGdtYWlsLmNvbQ==</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>面议</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1202125#reply0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>海外公司</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>远程工作</t>
         </is>
       </c>
-      <c r="D3" s="0" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[远程] 招聘航司逆向安全工程师</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>岗位职责：
+针对航司官网及移动端应用的通信协议进行安全审计与逆向分析
+研究主流航司的请求签名算法（如行业常见的 AK 系列、RE 系列参数体系及其衍生变种）
+持续跟踪航司安全策略迭代，维护技术方案的可用性
+与业务开发团队协作，定义数据接口规范</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>10K/月起（税前）</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1202059#reply6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>海外公司</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>后端开发</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[远程长期+合伙人] Go 后端 + WebRTC 技术负责人</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>岗位职责：
+我们有一套成熟的移动设备管理产品（ MDM ），已上线运营，
+目前用户量稳定增长，现有技术架构面临性能和维护瓶颈，
+决定进行全面技术升级重构。
+━━━━━━━━━━━━━━━━━━━━━━
+当前架构 → 目标架构
+服务端：PHP + Node.js  →  Go （统一单服务）
+通信层：纯 WebSocket  →  WebRTC + WebSocket 双协议
+VB.NET</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>面议</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Telegram: reSQL</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1202024#reply6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Atria 是一家基于人工智能的广告创意管理平台</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>前端开发</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[远程][外企] Atria 招聘 测试兼职/前端/产品</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>岗位职责：
+Atria 是一家基于人工智能的广告创意管理平台，致力于帮助营销人员更高效地创作高表现广告，从而提升 Meta 和 TikTok 等平台的广告投放效果。我们服务于众多知名公司，包括 Perplexity, ClickUp, Beehiiv, True Classic 。
+公司已完成天使轮融资，创立三年多，目前公司收月入远大于每月各方面支出，营收还在不断高速增长中。
+工作地点： 远程办公
+研发团队都是中国人，日常开发用中文交流即可。
+全远程工作，工作地点无要求，最好在亚太时区。
+研发 10 人，产品设计 3 人，团队成员主要来自腾讯、亚马逊和微软等国内外知名大厂。
+积极拥抱 AI ，公司给研发产品设计团队都提供 Codex 和 Claude Code 账号。
+1. 兼职测试工程师（每周≥3 天）</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>面议</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1201856#reply7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>海外公司</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>远程工作</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>一直想做的远程工作集合网站，上线了</t>
         </is>
       </c>
-      <c r="E3" s="0" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F3" s="0" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G3" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H3" s="0" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I3" s="0" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>岗位职责：
 前段时间找远程工作，横跳在各个平台之间，
@@ -1545,64 +1817,64 @@
 翻译成了中文</t>
         </is>
       </c>
-      <c r="J3" s="0" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K3" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L3" s="0" t="inlineStr">
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L7" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1201311#reply13</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>远程岗位</t>
         </is>
       </c>
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>后端开发</t>
         </is>
       </c>
-      <c r="D4" s="0" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>远程岗位：高级产品经理（AI 方向），广告接入技术支持工程师，远程 QA 测试工程师， PHP ， web， Flutter</t>
         </is>
       </c>
-      <c r="E4" s="0" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F4" s="0" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G4" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H4" s="0" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I4" s="0" t="inlineStr">
+      <c r="I8" s="0" t="inlineStr">
         <is>
           <t>岗位职责：
 1. 负责 AI 相关产品的规划、设计与迭代。
@@ -1624,64 +1896,64 @@
 * 技术壁垒： 通过沉淀针对各主流 CMS 的自动化接入方案，构建联盟在技术服务侧的竞争护城河。</t>
         </is>
       </c>
-      <c r="J4" s="0" t="inlineStr">
+      <c r="J8" s="0" t="inlineStr">
         <is>
           <t>50k+</t>
         </is>
       </c>
-      <c r="K4" s="0" t="inlineStr">
+      <c r="K8" s="0" t="inlineStr">
         <is>
           <t>Telegram: Skyewen20251</t>
         </is>
       </c>
-      <c r="L4" s="0" t="inlineStr">
+      <c r="L8" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1201527#reply1</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>外企招</t>
         </is>
       </c>
-      <c r="B5" s="0" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C5" s="0" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>后端开发</t>
         </is>
       </c>
-      <c r="D5" s="0" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>外企招聘数据工程师 20-50w/year (接受后端转)-full remote</t>
         </is>
       </c>
-      <c r="E5" s="0" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F5" s="0" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G5" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H5" s="0" t="inlineStr">
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I5" s="0" t="inlineStr">
+      <c r="I9" s="0" t="inlineStr">
         <is>
           <t>岗位职责：
 这是我之前发的招聘：
@@ -1694,957 +1966,709 @@
 公司简介，福利等见我之前的帖子，总体来说都还挺不错的。</t>
         </is>
       </c>
-      <c r="J5" s="0" t="inlineStr">
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K5" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L5" s="0" t="inlineStr">
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L9" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1198745#reply4</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>远程岗位</t>
         </is>
       </c>
-      <c r="B6" s="0" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C6" s="0" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>后端开发</t>
         </is>
       </c>
-      <c r="D6" s="0" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>远程岗位：高级产品经理（AI 方向），广告接入技术支持工程师，远程 QA 测试工程师， PHP ， web， Flutter</t>
         </is>
       </c>
-      <c r="E6" s="0" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F6" s="0" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G6" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H6" s="0" t="inlineStr">
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I6" s="0" t="inlineStr">
+      <c r="I10" s="0" t="inlineStr">
         <is>
           <t>岗位职责：1. 负责 AI 相关产品的规划、设计与迭代。；2. 结合公司业务方向，挖掘 AI 在业务场景中的落地机会。；3. 输出高质量 PRD 、流程图、原型图及需求说明文档。；4. 协同研发、设计、运营团队推进项目落地，确保版本按时高质量交付。；5. 跟踪行业动态、竞争产品与技术趋势，持续提出产品优化与创新方案。
 任职要求：1.  前端基础： 扎实的 HTML/JavaScript 功底，能熟练使用 Chrome DevTools 进行断点调试与网络层请求分析。；2.  CMS 经验： 深度熟悉 WordPress 钩子机制 (Hooks)**、AppleCMS 模板逻辑或类似内容的二次开发。；3.  **安全模型： 熟悉浏览器安全模型（**CORS 、CSP 、Sandbox**）及常见的广告拦截（ AdBlock ）对抗原理。；4.  专业加分： 有 Ad Network (广告联盟) 实际接入经验，或对 HTTP 协议、CDN 调优有深入理解。；5.  沟通能力： 具备“技术+服务”意识，能将复杂技术问题转化为易于站长理解的可执行方案。</t>
         </is>
       </c>
-      <c r="J6" s="0" t="inlineStr">
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t>50k+</t>
         </is>
       </c>
-      <c r="K6" s="0" t="inlineStr">
+      <c r="K10" s="0" t="inlineStr">
         <is>
           <t>Skyewen20251</t>
         </is>
       </c>
-      <c r="L6" s="0" t="inlineStr">
+      <c r="L10" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1201527#reply1</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B7" s="0" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>后端开发</t>
         </is>
       </c>
-      <c r="D7" s="0" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>寻远程运维/后端工程师， AI 算力服务方向，长期合作</t>
         </is>
       </c>
-      <c r="E7" s="0" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F7" s="0" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G7" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H7" s="0" t="inlineStr">
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I7" s="0" t="inlineStr">
+      <c r="I11" s="0" t="inlineStr">
         <is>
           <t>详见原帖</t>
         </is>
       </c>
-      <c r="J7" s="0" t="inlineStr">
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K7" s="0" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
         <is>
           <t>微信: HongKong_China-</t>
         </is>
       </c>
-      <c r="L7" s="13" t="inlineStr">
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1201439#reply0</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>海外游戏公司招</t>
         </is>
       </c>
-      <c r="B8" s="0" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>运营</t>
         </is>
       </c>
-      <c r="D8" s="0" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>海外游戏公司招聘 2 个职位-渗透测试-安全运营</t>
         </is>
       </c>
-      <c r="E8" s="0" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F8" s="0" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H8" s="0" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I8" s="0" t="inlineStr">
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t>岗位职责：安全监控与日志分析；• 负责 Splunk 等 SIEM 平台的日常运营和优化，设计并实现安全日志收集、存储、分析策略；；• 监控各类安全日志，识别异常行为，分析安全事件，提升检测能力；；• 创建并维护 SIEM 规则、仪表盘、告警策略，提高威胁检测效率。；应急响应与事件处置
 任职要求：熟悉 Splunk 等 SIEM 平台的部署、管理、规则编写及告警优化，有 Splunk ES （ Enterprise Security ）经验者优先；；具备安全事件分析与应急响应能力，熟悉 APT 攻击分析、恶意代码分析、网络入侵溯源等技术；；熟悉主流云计算平台的安全架构、日志分析和防护机制；熟悉常见安全框架和标准，如 MITRE ATT&amp;CK 、CIS 、NIST 、ISO 27001；具备一定的编程能力（ Python 、java 、Bash 等），能够开发安全自动化工具；</t>
         </is>
       </c>
-      <c r="J8" s="0" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K8" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L12" s="13" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200917#reply1</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="0" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B9" s="0" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C9" s="0" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>远程工作</t>
         </is>
       </c>
-      <c r="D9" s="0" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>远程工作网站开放</t>
         </is>
       </c>
-      <c r="E9" s="0" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F9" s="0" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G9" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H9" s="0" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I9" s="0" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>详见原帖</t>
         </is>
       </c>
-      <c r="J9" s="0" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K9" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L9" s="0" t="inlineStr">
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L13" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200863#reply10</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="0" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B10" s="0" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C10" s="0" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>AI/算法</t>
         </is>
       </c>
-      <c r="D10" s="0" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>AI 创业团队找一位运维开发工程师！</t>
         </is>
       </c>
-      <c r="E10" s="0" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F10" s="0" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I10" s="0" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>岗位职责：搭建并维护 CI/CD 流水线，基于 Github Action 、Gitlab CI/CD 等工具实现代码自动构建、测试与部署；；负责 Docker 镜像构建与优化，制定镜像规范，减少镜像体积，提升构建效率；；管理和维护 Kubernetes 集群（包括部署、扩缩容、监控告警、故障排查），保障集群稳定运行；；推进微服务架构下的容器化部署方案，制定服务发现、配置管理、灰度发布等策略；；负责多 Agent 系统的部署、编排与运维，确保各 Agent 服务的高可用与可观测性；
 任职要求：熟悉使用常见的代码仓库和配套组件，包括但不限于 Github 、Github Action 、Gitlab 、Gitlab Runner 等，能独立完成流水线搭建与维护；；精通 DevOps 理念与实践，掌握 Docker 镜像优化（多阶段构建、层缓存策略等），熟练进行 K8s 集群管理与容器化部署；；熟悉微服务架构设计与治理，具备多 Agent 系统的管理、部署与运维经验。</t>
         </is>
       </c>
-      <c r="J10" s="0" t="inlineStr">
+      <c r="J14" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K10" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L10" s="0" t="inlineStr">
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L14" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200637#reply5</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B11" s="0" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C11" s="0" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>全栈开发</t>
         </is>
       </c>
-      <c r="D11" s="0" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>[招聘-接受远程] AGI 全栈工程师（AI Agent / IoT-RTC）</t>
         </is>
       </c>
-      <c r="E11" s="0" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F11" s="0" t="inlineStr">
+      <c r="F15" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H11" s="0" t="inlineStr">
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I11" s="0" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>岗位职责：我们要做的，是把 AI 真正接入 IoT 世界：让摄像头能理解画面、让设备能听懂指令、让海量视频数据产生业务价值，是客户真正在用、愿意付费的产品功能。；- 将视觉 AI （人形检测、包裹识别、异常行为分析）、LLM （视频摘要、指令交互）、语音 AI 集成进 Ti RTC 平台，打造有付费价值的 AI 增值服务；- 独立负责 AI 功能全链路工程化：模型/API 选型、接口封装、异步调度、结果缓存、效果监控，对生产稳定性负责；- 主导 AI 场景技术评估，判断哪些场景值得做、评估精度/延迟/成本的平衡点，不做无效集成；- 将 AI 工具用到极致，同时推动 AI 在团队研发流程中的深度落地
 任职要求：- 出色的代码能力，语言不限（ Python / Go 均可）；- 有将 AI 能力集成进真实产品的工程经验（有真实用户在使用、效果可度量，不是内部工具或 Demo ）；- 能独立完成从需求评估、技术选型到生产上线的完整链路，对效果和稳定性负责；- 本人就是 AI 工具的重度用户：日常使用 Cursor / Claude Code 等工具开发，能清晰描述 AI 如何改变了你的</t>
         </is>
       </c>
-      <c r="J11" s="0" t="inlineStr">
+      <c r="J15" s="0" t="inlineStr">
         <is>
           <t>20K–45K ，根据能力面议</t>
         </is>
       </c>
-      <c r="K11" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L11" s="0" t="inlineStr">
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L15" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200788#reply0</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="0" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B12" s="0" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C12" s="0" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>区块链</t>
         </is>
       </c>
-      <c r="D12" s="0" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>HR 直招：🔥区块链高级安全工程师 - 远程 remote 办公</t>
         </is>
       </c>
-      <c r="E12" s="0" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F12" s="0" t="inlineStr">
+      <c r="F16" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G12" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H12" s="0" t="inlineStr">
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I12" s="0" t="inlineStr">
+      <c r="I16" s="0" t="inlineStr">
         <is>
           <t>岗位职责：- 全链路安全审计： 负责对区块链业务全链路进行安全评估与渗透测试。；- 智能合约安全： 负责智能合约的代码安全审计。；- 基础与云安全运营： 参与云端服务及终端环境的渗透测试与安全加固。
 任职要求：- 本科及以上学历优先，计算机、信息安全或网络安全等相关专业更佳。；- 具备 3-5 年相关工作经验，尤其是在信息安全或区块链安全相关领域具有实战经验。；- 熟悉区块链底层系统架构及智能合约相关知识；熟悉 Web3 领域常见的攻击手法及对应的防御策略（熟练使用 Slither 、Mythril 、Echidna 等合约审计与测试工具，熟悉 Foundry / Hardhat 等环境）。；- 具备扎实的网络安全功底，熟练掌握渗透测试、漏洞挖掘、网络流量分析及恶意代码分析等常规安全技能（熟练掌握 Burp Suite 、Nmap 、Wireshark 、IDA Pro 等行业主流攻防与分析工具）。；- 有大型安全项目的参与或落地经验，具备独立排查并解决实际安全问题的能力；在云环境的安全攻防方面具备一定的实操经验。</t>
         </is>
       </c>
-      <c r="J12" s="0" t="inlineStr">
+      <c r="J16" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K12" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L12" s="0" t="inlineStr">
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L16" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200785#reply0</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="0" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B13" s="0" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C13" s="0" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>AI/算法</t>
         </is>
       </c>
-      <c r="D13" s="0" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>[远程工作] Web3 交易所招 AI 落地工程师啦～～薪资待遇可谈</t>
         </is>
       </c>
-      <c r="E13" s="0" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F13" s="0" t="inlineStr">
+      <c r="F17" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G13" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H13" s="0" t="inlineStr">
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I13" s="0" t="inlineStr">
+      <c r="I17" s="0" t="inlineStr">
         <is>
           <t>岗位职责：APP 产品 AI 化（提升交易活跃度与用户粘性）；智能交易助手： 负责开发 AI 辅助交易功能（如基于自然语言的指令下单、智能止盈止损策略建议）。；行情辅助决策： 利用大模型（ LLM ）集成多源信息（新闻、推特情绪、链上数据），为用户提供实时研报、代币分析及风险预警。；个性化推荐： 基于用户交易行为，利用机器学习模型进行个性化的币种推荐、策略跟单推荐及投教内容分发。；客服机器人 2.0： 将传统的规则引擎客服升级为基于 RAG （检索增强生成）的 AI 客服，处理 80% 以上的复杂业务咨询。
 任职要求：教育背景（ Education ）；名校毕业，技术专业；工作经验（ Experience ）；3-5 年加密货币交易所、量化交易或金融科技（ Fintech ）产品经验，对交易所业务模型（现货、合约、流动性）有深刻理解。学习和工作经历能够证明对 LLM 和 ai agent 有足够的了解，最近经历涉及 workflow 的智能化改造并且有成功经验；能力与技能（ Skills &amp; Competencies ）</t>
         </is>
       </c>
-      <c r="J13" s="0" t="inlineStr">
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K13" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L13" s="0" t="inlineStr">
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L17" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200784#reply0</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="0" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>PB</t>
         </is>
       </c>
-      <c r="B14" s="0" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C14" s="0" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>AI/算法</t>
         </is>
       </c>
-      <c r="D14" s="0" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>远程大数据开发，推荐算法工程师，有兴趣可以聊聊</t>
         </is>
       </c>
-      <c r="E14" s="0" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F14" s="0" t="inlineStr">
+      <c r="F18" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G14" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H14" s="0" t="inlineStr">
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H18" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I14" s="0" t="inlineStr">
+      <c r="I18" s="0" t="inlineStr">
         <is>
           <t>详见原帖</t>
         </is>
       </c>
-      <c r="J14" s="0" t="inlineStr">
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t>25k-45k</t>
         </is>
       </c>
-      <c r="K14" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L14" s="0" t="inlineStr">
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L18" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200673#reply0</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="0" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B15" s="0" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C15" s="0" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>后端开发</t>
         </is>
       </c>
-      <c r="D15" s="0" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>golang 后端兼职—跨境电商 SaaS+AI</t>
         </is>
       </c>
-      <c r="E15" s="0" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F15" s="0" t="inlineStr">
+      <c r="F19" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G15" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H15" s="0" t="inlineStr">
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I15" s="0" t="inlineStr">
+      <c r="I19" s="0" t="inlineStr">
         <is>
           <t>岗位职责：岗位：Golang 后端工程师；*工作地点：深圳坂田；薪资：固定薪资+ 期权（面议）；团队规模：10 人创业团队，产品/技术/市场/运营齐备；参与后端架构设计与核心模块开发，保证 API 高可用、高并发。</t>
         </is>
       </c>
-      <c r="J15" s="0" t="inlineStr">
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>固定薪资+ 期权（面议）</t>
         </is>
       </c>
-      <c r="K15" s="0" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t>微信: godhaveajoke
 reSQL</t>
         </is>
       </c>
-      <c r="L15" s="0" t="inlineStr">
+      <c r="L19" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200518#reply7</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="0" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B16" s="0" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C16" s="0" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>UI/UX设计</t>
         </is>
       </c>
-      <c r="D16" s="0" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>[远程] 招聘 中高级 UI/UX 设计师！</t>
         </is>
       </c>
-      <c r="E16" s="0" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F16" s="0" t="inlineStr">
+      <c r="F20" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G16" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H16" s="0" t="inlineStr">
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H20" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I16" s="0" t="inlineStr">
+      <c r="I20" s="0" t="inlineStr">
         <is>
           <t>岗位职责：负责相机 App 整体视觉风格定位，完成首页、拍摄页、相册页、设置页等所有静态页面的 UI 设计，确保视觉效果贴合相机产品定位，兼具美观性与实用性。；主导相机 App 用户体验流程设计，梳理拍摄、预览、修图、分享等核心操作逻辑，完成交互原型设计，优化用户操作路径，提升产品易用性与流畅度。；Material Design 设计规范；，把控界面布局、色彩搭配、图标设计、字体排版等基础设计细节，保证产品设计的统一性与规范性。；负责相机 App 关键场景动效设计，包括拍摄快门动效、滤镜切换动效、页面转场动效、操作反馈动效等，通过优质动效提升产品质感与用户交互体验。
 任职要求：大专及以上学历，设计相关专业（视觉传达、数字媒体、工业设计等），1-3 年及以上 UI/UX 设计相关工作经验，有相机类、摄影类 App 设计经验者优先。；精通 Material Design 设计规范；，熟练掌握 UI 设计基础规范，对界面布局、色彩系统、组件设计、交互逻辑有深刻理解，能独立完成符合规范的设计作品。；具备扎实的静态页面设计能力，熟练使用 Figma 、Sketch 、PS 、AI 等设计工具，能高效输出高质量视觉设计稿，审美在线，擅长简约、质感类设计风格。；掌握动效设计技能，熟悉 AE 、Principle 等动效设计工具，能独立完成流畅、贴合产品场景的动效设计，懂基础交互逻辑与动效原理。</t>
         </is>
       </c>
-      <c r="J16" s="0" t="inlineStr">
+      <c r="J20" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K16" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L16" s="0" t="inlineStr">
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L20" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200541#reply0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="inlineStr">
-        <is>
-          <t>海外公司</t>
-        </is>
-      </c>
-      <c r="B17" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C17" s="0" t="inlineStr">
-        <is>
-          <t>UI/UX设计</t>
-        </is>
-      </c>
-      <c r="D17" s="0" t="inlineStr">
-        <is>
-          <t>Unlimit Pro is hiring Talent Acquisition Manager</t>
-        </is>
-      </c>
-      <c r="E17" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F17" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G17" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H17" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I17" s="0" t="inlineStr">
-        <is>
-          <t>详见原帖</t>
-        </is>
-      </c>
-      <c r="J17" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K17" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L17" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1200738#reply0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="inlineStr">
-        <is>
-          <t>海外公司</t>
-        </is>
-      </c>
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C18" s="0" t="inlineStr">
-        <is>
-          <t>后端开发</t>
-        </is>
-      </c>
-      <c r="D18" s="0" t="inlineStr">
-        <is>
-          <t>招聘多模态搜索后端工程师， founding engineer</t>
-        </is>
-      </c>
-      <c r="E18" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F18" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G18" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H18" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I18" s="0" t="inlineStr">
-        <is>
-          <t>详见原帖</t>
-        </is>
-      </c>
-      <c r="J18" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K18" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L18" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1200228#reply2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="inlineStr">
-        <is>
-          <t>海外公司</t>
-        </is>
-      </c>
-      <c r="B19" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C19" s="0" t="inlineStr">
-        <is>
-          <t>AI/算法</t>
-        </is>
-      </c>
-      <c r="D19" s="0" t="inlineStr">
-        <is>
-          <t>招两个远程工作，熟练基于开源大模型文本训练，视频训练的岗位</t>
-        </is>
-      </c>
-      <c r="E19" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F19" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G19" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H19" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I19" s="0" t="inlineStr">
-        <is>
-          <t>详见原帖</t>
-        </is>
-      </c>
-      <c r="J19" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K19" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L19" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1200008#reply4</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="inlineStr">
-        <is>
-          <t>BitFit</t>
-        </is>
-      </c>
-      <c r="B20" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C20" s="0" t="inlineStr">
-        <is>
-          <t>远程工作</t>
-        </is>
-      </c>
-      <c r="D20" s="0" t="inlineStr">
-        <is>
-          <t>BitFit 招聘（远程）</t>
-        </is>
-      </c>
-      <c r="E20" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F20" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G20" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H20" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I20" s="0" t="inlineStr">
-        <is>
-          <t>岗位职责：·  负责 MPC 钱包产品的整体规划，进行深入的市场、竞品及用户研究，定义产品定位、核心功能和长期发展路线图。；·  主导产品从概念、设计、开发、测试到上线、运营的全生命周期管理，撰写清晰的产品需求文档（ PRD ）和原型，并高效推动项目执行。；·  作为项目核心枢纽，高效协调研发、设计、市场、运营及安全团队，确保信息对齐、目标一致，并对最终的产品结果和用户体验负责。；·  建立并监控核心产品数据指标，通过用户反馈、行为数据及市场变化，持续推动产品优化与快速迭代。；·  紧密跟踪区块链、加密货币、钱包安全及 Web3 行业动态，将前沿趋势转化为产品机遇。</t>
-        </is>
-      </c>
-      <c r="J20" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K20" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L20" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1200330#reply0</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2685,12 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>产品经理</t>
+          <t>UI/UX设计</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>[远程][外企] Atria 招聘 多个研发岗位和产品设计师</t>
+          <t>Unlimit Pro is hiring Talent Acquisition Manager</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
@@ -2706,7 +2730,7 @@
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1199798#reply9</t>
+          <t>https://www.v2ex.com/t/1200738#reply0</t>
         </is>
       </c>
     </row>
@@ -2723,12 +2747,12 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>AI/算法</t>
+          <t>后端开发</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>[全职远程工作 ] AI 翻译/个人知识助手应用 iOS/Android 开发（限 3 ～ 5 年工作经验）</t>
+          <t>招聘多模态搜索后端工程师， founding engineer</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
@@ -2768,7 +2792,7 @@
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1199498#reply3</t>
+          <t>https://www.v2ex.com/t/1200228#reply2</t>
         </is>
       </c>
     </row>
@@ -2785,114 +2809,362 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
+          <t>AI/算法</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>招两个远程工作，熟练基于开源大模型文本训练，视频训练的岗位</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F23" s="0" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t>详见原帖</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>面议</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L23" s="0" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1200008#reply4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>BitFit</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>远程工作</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>BitFit 招聘（远程）</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>岗位职责：·  负责 MPC 钱包产品的整体规划，进行深入的市场、竞品及用户研究，定义产品定位、核心功能和长期发展路线图。；·  主导产品从概念、设计、开发、测试到上线、运营的全生命周期管理，撰写清晰的产品需求文档（ PRD ）和原型，并高效推动项目执行。；·  作为项目核心枢纽，高效协调研发、设计、市场、运营及安全团队，确保信息对齐、目标一致，并对最终的产品结果和用户体验负责。；·  建立并监控核心产品数据指标，通过用户反馈、行为数据及市场变化，持续推动产品优化与快速迭代。；·  紧密跟踪区块链、加密货币、钱包安全及 Web3 行业动态，将前沿趋势转化为产品机遇。</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>面议</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L24" s="0" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1200330#reply0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>海外公司</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>产品经理</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>[远程][外企] Atria 招聘 多个研发岗位和产品设计师</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F25" s="0" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t>详见原帖</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>面议</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L25" s="0" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1199798#reply9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>海外公司</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>AI/算法</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>[全职远程工作 ] AI 翻译/个人知识助手应用 iOS/Android 开发（限 3 ～ 5 年工作经验）</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F26" s="0" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
+          <t>详见原帖</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t>面议</t>
+        </is>
+      </c>
+      <c r="K26" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L26" s="0" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1199498#reply3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>海外公司</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
           <t>前端开发</t>
         </is>
       </c>
-      <c r="D23" s="0" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>[全职远程] AI-Native Java /React 全栈工程师</t>
         </is>
       </c>
-      <c r="E23" s="0" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F23" s="0" t="inlineStr">
+      <c r="F27" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G23" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H23" s="0" t="inlineStr">
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H27" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I23" s="0" t="inlineStr">
+      <c r="I27" s="0" t="inlineStr">
         <is>
           <t>岗位职责：参与该产品 V2.0 的需求分析、方案设计与研发交付，使用 Ai-native 的方式，负责从前端到后端的端到端实现（接口、数据模型、页面、联调与上线）。；基于 V1.0 的项目，使用 AI 编程工具，开发与维护核心业务模块：元数据采集/管理、数据发现与检索、服务请求与审批工作流、订阅/成本/授权（ Inventory ）管理等功能。；设计并实现高质量的 API 与领域模型，确保可维护性、可扩展性与可测试性（遵循 DDD / SOLID 等原则）。；使用并沉淀 AI 辅助研发与“Vibe Coding”工作流：用 AI 提升效率，同时通过测试与工程规范保证质量。
 任职要求：沟通主动积极，有良好的职业素养、工作习惯和团队意识；能独立推进任务闭环。；良好的英语读写能力（能阅读英文技术文档、进行基本技术沟通）。；4 年以上开发经验，具备全栈交付能力（能同时覆盖后端与前端关键链路），对“工程化交付”有较强意识。；AI-Native / Vibe Coding；熟练使用 AI 编程工具（如 Codex ，Claude Code ）完成：</t>
         </is>
       </c>
-      <c r="J23" s="0" t="inlineStr">
+      <c r="J27" s="0" t="inlineStr">
         <is>
           <t>15-25k</t>
         </is>
       </c>
-      <c r="K23" s="0" t="inlineStr">
+      <c r="K27" s="0" t="inlineStr">
         <is>
           <t>微信: base64
 reSQL</t>
         </is>
       </c>
-      <c r="L23" s="0" t="inlineStr">
+      <c r="L27" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1199537#reply1</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="0" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>外企招</t>
         </is>
       </c>
-      <c r="B24" s="0" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C24" s="0" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>后端开发</t>
         </is>
       </c>
-      <c r="D24" s="0" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>外企招聘数据工程师 20-50w/year (接受后端转)-full remote</t>
         </is>
       </c>
-      <c r="E24" s="0" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F24" s="0" t="inlineStr">
+      <c r="F28" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G24" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H24" s="0" t="inlineStr">
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H28" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I24" s="0" t="inlineStr">
+      <c r="I28" s="0" t="inlineStr">
         <is>
           <t>详见原帖</t>
         </is>
       </c>
-      <c r="J24" s="0" t="inlineStr">
+      <c r="J28" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K24" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L24" s="0" t="inlineStr">
+      <c r="K28" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L28" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1198745#reply3</t>
         </is>

--- a/money.xlsx
+++ b/money.xlsx
@@ -1401,7 +1401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col width="23.5576923076923" customWidth="1" style="1" min="1" max="1"/>
@@ -1764,47 +1764,390 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B7" s="0" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>后端开发</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>golang 后端兼职—跨境电商 SaaS+AI</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>岗位职责：
+岗位：Golang 后端工程师
+*工作地点：深圳坂田
+薪资：固定薪资+ 期权（面议）
+团队规模：10 人创业团队，产品/技术/市场/运营齐备
+参与后端架构设计与核心模块开发，保证 API 高可用、高并发。
+负责数据模型、MySQL / Redis / MongoDB 优化和维护。
+搭建并维护基础 AI 推理服务（模型部署、监控、告警）。
+实现多 Agent 协同与任务调度，确保业务流程顺畅。</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>固定薪资+ 期权（面议）</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>微信: godhaveajoke
+Telegram: reSQL</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1200518#reply8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>海外公司</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>市场营销</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>广告接入技术支持工程师
+30k 在家 办公</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>岗位职责：
+1.  深度支持接入： 指导站长在 WP (Hooks/Footer/Plugin)、AppleCMS 、Z-Blog 等各类复杂 CMS 环境下完成广告代码的**高性能植入**。
+2.  技术故障攻坚： 独立定位并排查 JS 报错、CSS 布局塌陷、Iframe 权限限制**及 **CDN 缓存同步**等接入难题。
+3.  **环境适配优化： 针对不同浏览器内核及广告拦截器（ AdBlocker ），提供**代码混淆、动态注入或域名反代**等技术绕过与兼容性建议。  Ym9iY3J0Z3ZzQGdtYWlsLmNvbQ==</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>面议</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L8" s="0" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1202125#reply0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>海外公司</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>远程工作</t>
         </is>
       </c>
-      <c r="D7" s="0" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>[远程] 招聘航司逆向安全工程师</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>岗位职责：
+针对航司官网及移动端应用的通信协议进行安全审计与逆向分析
+研究主流航司的请求签名算法（如行业常见的 AK 系列、RE 系列参数体系及其衍生变种）
+持续跟踪航司安全策略迭代，维护技术方案的可用性
+与业务开发团队协作，定义数据接口规范</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>10K/月起（税前）</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L9" s="0" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1202059#reply6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>海外公司</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>后端开发</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>[远程长期+合伙人] Go 后端 + WebRTC 技术负责人</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>岗位职责：
+我们有一套成熟的移动设备管理产品（ MDM ），已上线运营，
+目前用户量稳定增长，现有技术架构面临性能和维护瓶颈，
+决定进行全面技术升级重构。
+━━━━━━━━━━━━━━━━━━━━━━
+当前架构 → 目标架构
+服务端：PHP + Node.js  →  Go （统一单服务）
+通信层：纯 WebSocket  →  WebRTC + WebSocket 双协议
+VB.NET</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>面议</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>Telegram: reSQL</t>
+        </is>
+      </c>
+      <c r="L10" s="0" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1202024#reply6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>Atria 是一家基于人工智能的广告创意管理平台</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>前端开发</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>[远程][外企] Atria 招聘 测试兼职/前端/产品</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>岗位职责：
+Atria 是一家基于人工智能的广告创意管理平台，致力于帮助营销人员更高效地创作高表现广告，从而提升 Meta 和 TikTok 等平台的广告投放效果。我们服务于众多知名公司，包括 Perplexity, ClickUp, Beehiiv, True Classic 。
+公司已完成天使轮融资，创立三年多，目前公司收月入远大于每月各方面支出，营收还在不断高速增长中。
+工作地点： 远程办公
+研发团队都是中国人，日常开发用中文交流即可。
+全远程工作，工作地点无要求，最好在亚太时区。
+研发 10 人，产品设计 3 人，团队成员主要来自腾讯、亚马逊和微软等国内外知名大厂。
+积极拥抱 AI ，公司给研发产品设计团队都提供 Codex 和 Claude Code 账号。
+1. 兼职测试工程师（每周≥3 天）</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>面议</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L11" s="0" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1201856#reply7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>海外公司</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>远程工作</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>一直想做的远程工作集合网站，上线了</t>
         </is>
       </c>
-      <c r="E7" s="0" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F7" s="0" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G7" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H7" s="0" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I7" s="0" t="inlineStr">
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t>岗位职责：
 前段时间找远程工作，横跳在各个平台之间，
@@ -1817,64 +2160,64 @@
 翻译成了中文</t>
         </is>
       </c>
-      <c r="J7" s="0" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K7" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L7" s="0" t="inlineStr">
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L12" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1201311#reply13</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>远程岗位</t>
         </is>
       </c>
-      <c r="B8" s="0" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>后端开发</t>
         </is>
       </c>
-      <c r="D8" s="0" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>远程岗位：高级产品经理（AI 方向），广告接入技术支持工程师，远程 QA 测试工程师， PHP ， web， Flutter</t>
         </is>
       </c>
-      <c r="E8" s="0" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F8" s="0" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H8" s="0" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I8" s="0" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>岗位职责：
 1. 负责 AI 相关产品的规划、设计与迭代。
@@ -1896,64 +2239,64 @@
 * 技术壁垒： 通过沉淀针对各主流 CMS 的自动化接入方案，构建联盟在技术服务侧的竞争护城河。</t>
         </is>
       </c>
-      <c r="J8" s="0" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>50k+</t>
         </is>
       </c>
-      <c r="K8" s="0" t="inlineStr">
+      <c r="K13" s="0" t="inlineStr">
         <is>
           <t>Telegram: Skyewen20251</t>
         </is>
       </c>
-      <c r="L8" s="0" t="inlineStr">
+      <c r="L13" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1201527#reply1</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="0" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>外企招</t>
         </is>
       </c>
-      <c r="B9" s="0" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C9" s="0" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>后端开发</t>
         </is>
       </c>
-      <c r="D9" s="0" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>外企招聘数据工程师 20-50w/year (接受后端转)-full remote</t>
         </is>
       </c>
-      <c r="E9" s="0" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F9" s="0" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G9" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H9" s="0" t="inlineStr">
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I9" s="0" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>岗位职责：
 这是我之前发的招聘：
@@ -1966,1019 +2309,709 @@
 公司简介，福利等见我之前的帖子，总体来说都还挺不错的。</t>
         </is>
       </c>
-      <c r="J9" s="0" t="inlineStr">
+      <c r="J14" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K9" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L9" s="0" t="inlineStr">
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L14" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1198745#reply4</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="0" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>远程岗位</t>
         </is>
       </c>
-      <c r="B10" s="0" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C10" s="0" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>后端开发</t>
         </is>
       </c>
-      <c r="D10" s="0" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>远程岗位：高级产品经理（AI 方向），广告接入技术支持工程师，远程 QA 测试工程师， PHP ， web， Flutter</t>
         </is>
       </c>
-      <c r="E10" s="0" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F10" s="0" t="inlineStr">
+      <c r="F15" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I10" s="0" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>岗位职责：1. 负责 AI 相关产品的规划、设计与迭代。；2. 结合公司业务方向，挖掘 AI 在业务场景中的落地机会。；3. 输出高质量 PRD 、流程图、原型图及需求说明文档。；4. 协同研发、设计、运营团队推进项目落地，确保版本按时高质量交付。；5. 跟踪行业动态、竞争产品与技术趋势，持续提出产品优化与创新方案。
 任职要求：1.  前端基础： 扎实的 HTML/JavaScript 功底，能熟练使用 Chrome DevTools 进行断点调试与网络层请求分析。；2.  CMS 经验： 深度熟悉 WordPress 钩子机制 (Hooks)**、AppleCMS 模板逻辑或类似内容的二次开发。；3.  **安全模型： 熟悉浏览器安全模型（**CORS 、CSP 、Sandbox**）及常见的广告拦截（ AdBlock ）对抗原理。；4.  专业加分： 有 Ad Network (广告联盟) 实际接入经验，或对 HTTP 协议、CDN 调优有深入理解。；5.  沟通能力： 具备“技术+服务”意识，能将复杂技术问题转化为易于站长理解的可执行方案。</t>
         </is>
       </c>
-      <c r="J10" s="0" t="inlineStr">
+      <c r="J15" s="0" t="inlineStr">
         <is>
           <t>50k+</t>
         </is>
       </c>
-      <c r="K10" s="0" t="inlineStr">
+      <c r="K15" s="0" t="inlineStr">
         <is>
           <t>Skyewen20251</t>
         </is>
       </c>
-      <c r="L10" s="0" t="inlineStr">
+      <c r="L15" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1201527#reply1</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B11" s="0" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C11" s="0" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>后端开发</t>
         </is>
       </c>
-      <c r="D11" s="0" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>寻远程运维/后端工程师， AI 算力服务方向，长期合作</t>
         </is>
       </c>
-      <c r="E11" s="0" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F11" s="0" t="inlineStr">
+      <c r="F16" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H11" s="0" t="inlineStr">
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I11" s="0" t="inlineStr">
+      <c r="I16" s="0" t="inlineStr">
         <is>
           <t>详见原帖</t>
         </is>
       </c>
-      <c r="J11" s="0" t="inlineStr">
+      <c r="J16" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K11" s="0" t="inlineStr">
+      <c r="K16" s="0" t="inlineStr">
         <is>
           <t>微信: HongKong_China-</t>
         </is>
       </c>
-      <c r="L11" s="13" t="inlineStr">
+      <c r="L16" s="13" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1201439#reply0</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="0" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>海外游戏公司招</t>
         </is>
       </c>
-      <c r="B12" s="0" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C12" s="0" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>运营</t>
         </is>
       </c>
-      <c r="D12" s="0" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>海外游戏公司招聘 2 个职位-渗透测试-安全运营</t>
         </is>
       </c>
-      <c r="E12" s="0" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F12" s="0" t="inlineStr">
+      <c r="F17" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G12" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H12" s="0" t="inlineStr">
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I12" s="0" t="inlineStr">
+      <c r="I17" s="0" t="inlineStr">
         <is>
           <t>岗位职责：安全监控与日志分析；• 负责 Splunk 等 SIEM 平台的日常运营和优化，设计并实现安全日志收集、存储、分析策略；；• 监控各类安全日志，识别异常行为，分析安全事件，提升检测能力；；• 创建并维护 SIEM 规则、仪表盘、告警策略，提高威胁检测效率。；应急响应与事件处置
 任职要求：熟悉 Splunk 等 SIEM 平台的部署、管理、规则编写及告警优化，有 Splunk ES （ Enterprise Security ）经验者优先；；具备安全事件分析与应急响应能力，熟悉 APT 攻击分析、恶意代码分析、网络入侵溯源等技术；；熟悉主流云计算平台的安全架构、日志分析和防护机制；熟悉常见安全框架和标准，如 MITRE ATT&amp;CK 、CIS 、NIST 、ISO 27001；具备一定的编程能力（ Python 、java 、Bash 等），能够开发安全自动化工具；</t>
         </is>
       </c>
-      <c r="J12" s="0" t="inlineStr">
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K12" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L12" s="13" t="inlineStr">
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200917#reply1</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="0" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B13" s="0" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C13" s="0" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>远程工作</t>
         </is>
       </c>
-      <c r="D13" s="0" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>远程工作网站开放</t>
         </is>
       </c>
-      <c r="E13" s="0" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F13" s="0" t="inlineStr">
+      <c r="F18" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G13" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H13" s="0" t="inlineStr">
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H18" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I13" s="0" t="inlineStr">
+      <c r="I18" s="0" t="inlineStr">
         <is>
           <t>详见原帖</t>
         </is>
       </c>
-      <c r="J13" s="0" t="inlineStr">
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K13" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L13" s="0" t="inlineStr">
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L18" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200863#reply10</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="0" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B14" s="0" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C14" s="0" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>AI/算法</t>
         </is>
       </c>
-      <c r="D14" s="0" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>AI 创业团队找一位运维开发工程师！</t>
         </is>
       </c>
-      <c r="E14" s="0" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F14" s="0" t="inlineStr">
+      <c r="F19" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G14" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H14" s="0" t="inlineStr">
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I14" s="0" t="inlineStr">
+      <c r="I19" s="0" t="inlineStr">
         <is>
           <t>岗位职责：搭建并维护 CI/CD 流水线，基于 Github Action 、Gitlab CI/CD 等工具实现代码自动构建、测试与部署；；负责 Docker 镜像构建与优化，制定镜像规范，减少镜像体积，提升构建效率；；管理和维护 Kubernetes 集群（包括部署、扩缩容、监控告警、故障排查），保障集群稳定运行；；推进微服务架构下的容器化部署方案，制定服务发现、配置管理、灰度发布等策略；；负责多 Agent 系统的部署、编排与运维，确保各 Agent 服务的高可用与可观测性；
 任职要求：熟悉使用常见的代码仓库和配套组件，包括但不限于 Github 、Github Action 、Gitlab 、Gitlab Runner 等，能独立完成流水线搭建与维护；；精通 DevOps 理念与实践，掌握 Docker 镜像优化（多阶段构建、层缓存策略等），熟练进行 K8s 集群管理与容器化部署；；熟悉微服务架构设计与治理，具备多 Agent 系统的管理、部署与运维经验。</t>
         </is>
       </c>
-      <c r="J14" s="0" t="inlineStr">
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K14" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L14" s="0" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L19" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200637#reply5</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="0" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B15" s="0" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C15" s="0" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>全栈开发</t>
         </is>
       </c>
-      <c r="D15" s="0" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>[招聘-接受远程] AGI 全栈工程师（AI Agent / IoT-RTC）</t>
         </is>
       </c>
-      <c r="E15" s="0" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F15" s="0" t="inlineStr">
+      <c r="F20" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G15" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H15" s="0" t="inlineStr">
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H20" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I15" s="0" t="inlineStr">
+      <c r="I20" s="0" t="inlineStr">
         <is>
           <t>岗位职责：我们要做的，是把 AI 真正接入 IoT 世界：让摄像头能理解画面、让设备能听懂指令、让海量视频数据产生业务价值，是客户真正在用、愿意付费的产品功能。；- 将视觉 AI （人形检测、包裹识别、异常行为分析）、LLM （视频摘要、指令交互）、语音 AI 集成进 Ti RTC 平台，打造有付费价值的 AI 增值服务；- 独立负责 AI 功能全链路工程化：模型/API 选型、接口封装、异步调度、结果缓存、效果监控，对生产稳定性负责；- 主导 AI 场景技术评估，判断哪些场景值得做、评估精度/延迟/成本的平衡点，不做无效集成；- 将 AI 工具用到极致，同时推动 AI 在团队研发流程中的深度落地
 任职要求：- 出色的代码能力，语言不限（ Python / Go 均可）；- 有将 AI 能力集成进真实产品的工程经验（有真实用户在使用、效果可度量，不是内部工具或 Demo ）；- 能独立完成从需求评估、技术选型到生产上线的完整链路，对效果和稳定性负责；- 本人就是 AI 工具的重度用户：日常使用 Cursor / Claude Code 等工具开发，能清晰描述 AI 如何改变了你的</t>
         </is>
       </c>
-      <c r="J15" s="0" t="inlineStr">
+      <c r="J20" s="0" t="inlineStr">
         <is>
           <t>20K–45K ，根据能力面议</t>
         </is>
       </c>
-      <c r="K15" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L15" s="0" t="inlineStr">
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L20" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200788#reply0</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="0" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B16" s="0" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C16" s="0" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>区块链</t>
         </is>
       </c>
-      <c r="D16" s="0" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>HR 直招：🔥区块链高级安全工程师 - 远程 remote 办公</t>
         </is>
       </c>
-      <c r="E16" s="0" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F16" s="0" t="inlineStr">
+      <c r="F21" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G16" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H16" s="0" t="inlineStr">
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I16" s="0" t="inlineStr">
+      <c r="I21" s="0" t="inlineStr">
         <is>
           <t>岗位职责：- 全链路安全审计： 负责对区块链业务全链路进行安全评估与渗透测试。；- 智能合约安全： 负责智能合约的代码安全审计。；- 基础与云安全运营： 参与云端服务及终端环境的渗透测试与安全加固。
 任职要求：- 本科及以上学历优先，计算机、信息安全或网络安全等相关专业更佳。；- 具备 3-5 年相关工作经验，尤其是在信息安全或区块链安全相关领域具有实战经验。；- 熟悉区块链底层系统架构及智能合约相关知识；熟悉 Web3 领域常见的攻击手法及对应的防御策略（熟练使用 Slither 、Mythril 、Echidna 等合约审计与测试工具，熟悉 Foundry / Hardhat 等环境）。；- 具备扎实的网络安全功底，熟练掌握渗透测试、漏洞挖掘、网络流量分析及恶意代码分析等常规安全技能（熟练掌握 Burp Suite 、Nmap 、Wireshark 、IDA Pro 等行业主流攻防与分析工具）。；- 有大型安全项目的参与或落地经验，具备独立排查并解决实际安全问题的能力；在云环境的安全攻防方面具备一定的实操经验。</t>
         </is>
       </c>
-      <c r="J16" s="0" t="inlineStr">
+      <c r="J21" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K16" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L16" s="0" t="inlineStr">
+      <c r="K21" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L21" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200785#reply0</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="0" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B17" s="0" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C17" s="0" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>AI/算法</t>
         </is>
       </c>
-      <c r="D17" s="0" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>[远程工作] Web3 交易所招 AI 落地工程师啦～～薪资待遇可谈</t>
         </is>
       </c>
-      <c r="E17" s="0" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F17" s="0" t="inlineStr">
+      <c r="F22" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G17" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H17" s="0" t="inlineStr">
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I17" s="0" t="inlineStr">
+      <c r="I22" s="0" t="inlineStr">
         <is>
           <t>岗位职责：APP 产品 AI 化（提升交易活跃度与用户粘性）；智能交易助手： 负责开发 AI 辅助交易功能（如基于自然语言的指令下单、智能止盈止损策略建议）。；行情辅助决策： 利用大模型（ LLM ）集成多源信息（新闻、推特情绪、链上数据），为用户提供实时研报、代币分析及风险预警。；个性化推荐： 基于用户交易行为，利用机器学习模型进行个性化的币种推荐、策略跟单推荐及投教内容分发。；客服机器人 2.0： 将传统的规则引擎客服升级为基于 RAG （检索增强生成）的 AI 客服，处理 80% 以上的复杂业务咨询。
 任职要求：教育背景（ Education ）；名校毕业，技术专业；工作经验（ Experience ）；3-5 年加密货币交易所、量化交易或金融科技（ Fintech ）产品经验，对交易所业务模型（现货、合约、流动性）有深刻理解。学习和工作经历能够证明对 LLM 和 ai agent 有足够的了解，最近经历涉及 workflow 的智能化改造并且有成功经验；能力与技能（ Skills &amp; Competencies ）</t>
         </is>
       </c>
-      <c r="J17" s="0" t="inlineStr">
+      <c r="J22" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K17" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L17" s="0" t="inlineStr">
+      <c r="K22" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L22" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200784#reply0</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="0" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>PB</t>
         </is>
       </c>
-      <c r="B18" s="0" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C18" s="0" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>AI/算法</t>
         </is>
       </c>
-      <c r="D18" s="0" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>远程大数据开发，推荐算法工程师，有兴趣可以聊聊</t>
         </is>
       </c>
-      <c r="E18" s="0" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F18" s="0" t="inlineStr">
+      <c r="F23" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G18" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H18" s="0" t="inlineStr">
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H23" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I18" s="0" t="inlineStr">
+      <c r="I23" s="0" t="inlineStr">
         <is>
           <t>详见原帖</t>
         </is>
       </c>
-      <c r="J18" s="0" t="inlineStr">
+      <c r="J23" s="0" t="inlineStr">
         <is>
           <t>25k-45k</t>
         </is>
       </c>
-      <c r="K18" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L18" s="0" t="inlineStr">
+      <c r="K23" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L23" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200673#reply0</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="0" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B19" s="0" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C19" s="0" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>后端开发</t>
         </is>
       </c>
-      <c r="D19" s="0" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>golang 后端兼职—跨境电商 SaaS+AI</t>
         </is>
       </c>
-      <c r="E19" s="0" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F19" s="0" t="inlineStr">
+      <c r="F24" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G19" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H19" s="0" t="inlineStr">
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I19" s="0" t="inlineStr">
+      <c r="I24" s="0" t="inlineStr">
         <is>
           <t>岗位职责：岗位：Golang 后端工程师；*工作地点：深圳坂田；薪资：固定薪资+ 期权（面议）；团队规模：10 人创业团队，产品/技术/市场/运营齐备；参与后端架构设计与核心模块开发，保证 API 高可用、高并发。</t>
         </is>
       </c>
-      <c r="J19" s="0" t="inlineStr">
+      <c r="J24" s="0" t="inlineStr">
         <is>
           <t>固定薪资+ 期权（面议）</t>
         </is>
       </c>
-      <c r="K19" s="0" t="inlineStr">
+      <c r="K24" s="0" t="inlineStr">
         <is>
           <t>微信: godhaveajoke
 reSQL</t>
         </is>
       </c>
-      <c r="L19" s="0" t="inlineStr">
+      <c r="L24" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200518#reply7</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="0" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B20" s="0" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C20" s="0" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>UI/UX设计</t>
         </is>
       </c>
-      <c r="D20" s="0" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>[远程] 招聘 中高级 UI/UX 设计师！</t>
         </is>
       </c>
-      <c r="E20" s="0" t="inlineStr">
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F20" s="0" t="inlineStr">
+      <c r="F25" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G20" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H20" s="0" t="inlineStr">
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H25" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I20" s="0" t="inlineStr">
+      <c r="I25" s="0" t="inlineStr">
         <is>
           <t>岗位职责：负责相机 App 整体视觉风格定位，完成首页、拍摄页、相册页、设置页等所有静态页面的 UI 设计，确保视觉效果贴合相机产品定位，兼具美观性与实用性。；主导相机 App 用户体验流程设计，梳理拍摄、预览、修图、分享等核心操作逻辑，完成交互原型设计，优化用户操作路径，提升产品易用性与流畅度。；Material Design 设计规范；，把控界面布局、色彩搭配、图标设计、字体排版等基础设计细节，保证产品设计的统一性与规范性。；负责相机 App 关键场景动效设计，包括拍摄快门动效、滤镜切换动效、页面转场动效、操作反馈动效等，通过优质动效提升产品质感与用户交互体验。
 任职要求：大专及以上学历，设计相关专业（视觉传达、数字媒体、工业设计等），1-3 年及以上 UI/UX 设计相关工作经验，有相机类、摄影类 App 设计经验者优先。；精通 Material Design 设计规范；，熟练掌握 UI 设计基础规范，对界面布局、色彩系统、组件设计、交互逻辑有深刻理解，能独立完成符合规范的设计作品。；具备扎实的静态页面设计能力，熟练使用 Figma 、Sketch 、PS 、AI 等设计工具，能高效输出高质量视觉设计稿，审美在线，擅长简约、质感类设计风格。；掌握动效设计技能，熟悉 AE 、Principle 等动效设计工具，能独立完成流畅、贴合产品场景的动效设计，懂基础交互逻辑与动效原理。</t>
         </is>
       </c>
-      <c r="J20" s="0" t="inlineStr">
+      <c r="J25" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K20" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L20" s="0" t="inlineStr">
+      <c r="K25" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L25" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200541#reply0</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t>海外公司</t>
-        </is>
-      </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t>UI/UX设计</t>
-        </is>
-      </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t>Unlimit Pro is hiring Talent Acquisition Manager</t>
-        </is>
-      </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G21" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H21" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I21" s="0" t="inlineStr">
-        <is>
-          <t>详见原帖</t>
-        </is>
-      </c>
-      <c r="J21" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K21" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L21" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1200738#reply0</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="inlineStr">
-        <is>
-          <t>海外公司</t>
-        </is>
-      </c>
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t>后端开发</t>
-        </is>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t>招聘多模态搜索后端工程师， founding engineer</t>
-        </is>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H22" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I22" s="0" t="inlineStr">
-        <is>
-          <t>详见原帖</t>
-        </is>
-      </c>
-      <c r="J22" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K22" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L22" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1200228#reply2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0" t="inlineStr">
-        <is>
-          <t>海外公司</t>
-        </is>
-      </c>
-      <c r="B23" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C23" s="0" t="inlineStr">
-        <is>
-          <t>AI/算法</t>
-        </is>
-      </c>
-      <c r="D23" s="0" t="inlineStr">
-        <is>
-          <t>招两个远程工作，熟练基于开源大模型文本训练，视频训练的岗位</t>
-        </is>
-      </c>
-      <c r="E23" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F23" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G23" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H23" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I23" s="0" t="inlineStr">
-        <is>
-          <t>详见原帖</t>
-        </is>
-      </c>
-      <c r="J23" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K23" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L23" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1200008#reply4</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0" t="inlineStr">
-        <is>
-          <t>BitFit</t>
-        </is>
-      </c>
-      <c r="B24" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C24" s="0" t="inlineStr">
-        <is>
-          <t>远程工作</t>
-        </is>
-      </c>
-      <c r="D24" s="0" t="inlineStr">
-        <is>
-          <t>BitFit 招聘（远程）</t>
-        </is>
-      </c>
-      <c r="E24" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F24" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G24" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H24" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I24" s="0" t="inlineStr">
-        <is>
-          <t>岗位职责：·  负责 MPC 钱包产品的整体规划，进行深入的市场、竞品及用户研究，定义产品定位、核心功能和长期发展路线图。；·  主导产品从概念、设计、开发、测试到上线、运营的全生命周期管理，撰写清晰的产品需求文档（ PRD ）和原型，并高效推动项目执行。；·  作为项目核心枢纽，高效协调研发、设计、市场、运营及安全团队，确保信息对齐、目标一致，并对最终的产品结果和用户体验负责。；·  建立并监控核心产品数据指标，通过用户反馈、行为数据及市场变化，持续推动产品优化与快速迭代。；·  紧密跟踪区块链、加密货币、钱包安全及 Web3 行业动态，将前沿趋势转化为产品机遇。</t>
-        </is>
-      </c>
-      <c r="J24" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K24" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L24" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1200330#reply0</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0" t="inlineStr">
-        <is>
-          <t>海外公司</t>
-        </is>
-      </c>
-      <c r="B25" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C25" s="0" t="inlineStr">
-        <is>
-          <t>产品经理</t>
-        </is>
-      </c>
-      <c r="D25" s="0" t="inlineStr">
-        <is>
-          <t>[远程][外企] Atria 招聘 多个研发岗位和产品设计师</t>
-        </is>
-      </c>
-      <c r="E25" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F25" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G25" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H25" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I25" s="0" t="inlineStr">
-        <is>
-          <t>详见原帖</t>
-        </is>
-      </c>
-      <c r="J25" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K25" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L25" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1199798#reply9</t>
         </is>
       </c>
     </row>
@@ -2995,12 +3028,12 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>AI/算法</t>
+          <t>UI/UX设计</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t>[全职远程工作 ] AI 翻译/个人知识助手应用 iOS/Android 开发（限 3 ～ 5 年工作经验）</t>
+          <t>Unlimit Pro is hiring Talent Acquisition Manager</t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr">
@@ -3040,7 +3073,7 @@
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1199498#reply3</t>
+          <t>https://www.v2ex.com/t/1200738#reply0</t>
         </is>
       </c>
     </row>
@@ -3057,114 +3090,424 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
+          <t>后端开发</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>招聘多模态搜索后端工程师， founding engineer</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F27" s="0" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="inlineStr">
+        <is>
+          <t>详见原帖</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t>面议</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L27" s="0" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1200228#reply2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t>海外公司</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>AI/算法</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>招两个远程工作，熟练基于开源大模型文本训练，视频训练的岗位</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F28" s="0" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t>详见原帖</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>面议</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L28" s="0" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1200008#reply4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t>BitFit</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>远程工作</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="inlineStr">
+        <is>
+          <t>BitFit 招聘（远程）</t>
+        </is>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F29" s="0" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t>岗位职责：·  负责 MPC 钱包产品的整体规划，进行深入的市场、竞品及用户研究，定义产品定位、核心功能和长期发展路线图。；·  主导产品从概念、设计、开发、测试到上线、运营的全生命周期管理，撰写清晰的产品需求文档（ PRD ）和原型，并高效推动项目执行。；·  作为项目核心枢纽，高效协调研发、设计、市场、运营及安全团队，确保信息对齐、目标一致，并对最终的产品结果和用户体验负责。；·  建立并监控核心产品数据指标，通过用户反馈、行为数据及市场变化，持续推动产品优化与快速迭代。；·  紧密跟踪区块链、加密货币、钱包安全及 Web3 行业动态，将前沿趋势转化为产品机遇。</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
+        <is>
+          <t>面议</t>
+        </is>
+      </c>
+      <c r="K29" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L29" s="0" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1200330#reply0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t>海外公司</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>产品经理</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>[远程][外企] Atria 招聘 多个研发岗位和产品设计师</t>
+        </is>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F30" s="0" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="inlineStr">
+        <is>
+          <t>详见原帖</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="inlineStr">
+        <is>
+          <t>面议</t>
+        </is>
+      </c>
+      <c r="K30" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L30" s="0" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1199798#reply9</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>海外公司</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>AI/算法</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>[全职远程工作 ] AI 翻译/个人知识助手应用 iOS/Android 开发（限 3 ～ 5 年工作经验）</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F31" s="0" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="inlineStr">
+        <is>
+          <t>详见原帖</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="inlineStr">
+        <is>
+          <t>面议</t>
+        </is>
+      </c>
+      <c r="K31" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L31" s="0" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1199498#reply3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>海外公司</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
           <t>前端开发</t>
         </is>
       </c>
-      <c r="D27" s="0" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>[全职远程] AI-Native Java /React 全栈工程师</t>
         </is>
       </c>
-      <c r="E27" s="0" t="inlineStr">
+      <c r="E32" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F27" s="0" t="inlineStr">
+      <c r="F32" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G27" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H27" s="0" t="inlineStr">
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H32" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I27" s="0" t="inlineStr">
+      <c r="I32" s="0" t="inlineStr">
         <is>
           <t>岗位职责：参与该产品 V2.0 的需求分析、方案设计与研发交付，使用 Ai-native 的方式，负责从前端到后端的端到端实现（接口、数据模型、页面、联调与上线）。；基于 V1.0 的项目，使用 AI 编程工具，开发与维护核心业务模块：元数据采集/管理、数据发现与检索、服务请求与审批工作流、订阅/成本/授权（ Inventory ）管理等功能。；设计并实现高质量的 API 与领域模型，确保可维护性、可扩展性与可测试性（遵循 DDD / SOLID 等原则）。；使用并沉淀 AI 辅助研发与“Vibe Coding”工作流：用 AI 提升效率，同时通过测试与工程规范保证质量。
 任职要求：沟通主动积极，有良好的职业素养、工作习惯和团队意识；能独立推进任务闭环。；良好的英语读写能力（能阅读英文技术文档、进行基本技术沟通）。；4 年以上开发经验，具备全栈交付能力（能同时覆盖后端与前端关键链路），对“工程化交付”有较强意识。；AI-Native / Vibe Coding；熟练使用 AI 编程工具（如 Codex ，Claude Code ）完成：</t>
         </is>
       </c>
-      <c r="J27" s="0" t="inlineStr">
+      <c r="J32" s="0" t="inlineStr">
         <is>
           <t>15-25k</t>
         </is>
       </c>
-      <c r="K27" s="0" t="inlineStr">
+      <c r="K32" s="0" t="inlineStr">
         <is>
           <t>微信: base64
 reSQL</t>
         </is>
       </c>
-      <c r="L27" s="0" t="inlineStr">
+      <c r="L32" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1199537#reply1</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="0" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>外企招</t>
         </is>
       </c>
-      <c r="B28" s="0" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C28" s="0" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>后端开发</t>
         </is>
       </c>
-      <c r="D28" s="0" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>外企招聘数据工程师 20-50w/year (接受后端转)-full remote</t>
         </is>
       </c>
-      <c r="E28" s="0" t="inlineStr">
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F28" s="0" t="inlineStr">
+      <c r="F33" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G28" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H28" s="0" t="inlineStr">
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H33" s="0" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="I28" s="0" t="inlineStr">
+      <c r="I33" s="0" t="inlineStr">
         <is>
           <t>详见原帖</t>
         </is>
       </c>
-      <c r="J28" s="0" t="inlineStr">
+      <c r="J33" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K28" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L28" s="0" t="inlineStr">
+      <c r="K33" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L33" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1198745#reply3</t>
         </is>

--- a/money.xlsx
+++ b/money.xlsx
@@ -773,7 +773,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -805,9 +805,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1401,7 +1398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col width="23.5576923076923" customWidth="1" style="1" min="1" max="1"/>
@@ -1491,49 +1488,110 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" s="1">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MDM产品公司</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>前端开发</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Android 开发</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>内推岗</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>Android 系统级开发
+我们有一套已上线的企业移动设备管理（ MDM ）产品，用户量稳定增长，现需一位专注 Android 客户端深度适配的技术人才。
+职责：
+基于 AccessibilityService 开发设备自动化配置功能（权限引导、一键部署） 各品牌 ROM 深度适配：小米、Oppo 、Vivo 、Samsung 、Honor 、Realme 、传音系等，目前已覆盖 60+ 个品牌 Activity ，需持续维护和扩展 设备管理策略的合规性保障（防止终端用户误操作导致管理策略失效） 后台托管服务的稳定性优化（ Android 12~15 各版本适配） 系统级电源策略适配，确保管理服务不被系统休眠中断 必须有的经验：
+AccessibilityService 实际项目经验（不是 demo 级别的） 做过至少 3 个品牌的 ROM 适配 熟悉 Android 系统分析工具 有各品牌真机调试经验 加分项：
+做过 MDM / 企业设备管理类产品 有 Device Owner / Device Policy 开发经验 了解 Android Enterprise 相关标准 合作方式： 远程合作，按模块/任务计费，长期需求。服务端已有人负责，你只需专注 Android 客户端，按约定的指令协议实现功能。</t>
+        </is>
+      </c>
+      <c r="K3" s="0" t="inlineStr">
+        <is>
+          <t>telegram：lei2025</t>
+        </is>
+      </c>
+      <c r="L3" s="0" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1202057#reply0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1" s="1">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>市场营销</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>广告接入技术支持工程师
-30k 在家 办公</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>技术支持工程师</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
         <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t>岗位职责：
 1.  深度支持接入： 指导站长在 WP (Hooks/Footer/Plugin)、AppleCMS 、Z-Blog 等各类复杂 CMS 环境下完成广告代码的**高性能植入**。
@@ -1541,64 +1599,64 @@
 3.  **环境适配优化： 针对不同浏览器内核及广告拦截器（ AdBlocker ），提供**代码混淆、动态注入或域名反代**等技术绕过与兼容性建议。  Ym9iY3J0Z3ZzQGdtYWlsLmNvbQ==</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="K4" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L4" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1202125#reply0</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>远程工作</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>[远程] 招聘航司逆向安全工程师</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>逆向安全工程师</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="inlineStr">
         <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>岗位职责：
 针对航司官网及移动端应用的通信协议进行安全审计与逆向分析
@@ -1607,64 +1665,64 @@
 与业务开发团队协作，定义数据接口规范</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>10K/月起（税前）</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L5" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1202059#reply6</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>后端开发</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>[远程长期+合伙人] Go 后端 + WebRTC 技术负责人</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Go 后端 + WebRTC 技术负责人</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H6" s="0" t="inlineStr">
         <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" s="0" t="inlineStr">
         <is>
           <t>岗位职责：
 我们有一套成熟的移动设备管理产品（ MDM ），已上线运营，
@@ -1677,64 +1735,64 @@
 VB.NET</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t>Telegram: reSQL</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1202024#reply6</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Atria 是一家基于人工智能的广告创意管理平台</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>Atria</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>前端开发</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>[远程][外企] Atria 招聘 测试兼职/前端/产品</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>多岗位</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Atria 招聘 测试兼职/前端/产品</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
         <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>岗位职责：
 Atria 是一家基于人工智能的广告创意管理平台，致力于帮助营销人员更高效地创作高表现广告，从而提升 Meta 和 TikTok 等平台的广告投放效果。我们服务于众多知名公司，包括 Perplexity, ClickUp, Beehiiv, True Classic 。
@@ -1747,64 +1805,64 @@
 1. 兼职测试工程师（每周≥3 天）</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L7" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1201856#reply7</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>海外公司</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>后端开发</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>golang 后端兼职—跨境电商 SaaS+AI</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>golang 后端</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>内推岗</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
         <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" s="0" t="inlineStr">
         <is>
           <t>岗位职责：
 岗位：Golang 后端工程师
@@ -1817,86 +1875,20 @@
 实现多 Agent 协同与任务调度，确保业务流程顺畅。</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" s="0" t="inlineStr">
         <is>
           <t>固定薪资+ 期权（面议）</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K8" s="0" t="inlineStr">
         <is>
           <t>微信: godhaveajoke
 Telegram: reSQL</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L8" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1200518#reply8</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>海外公司</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>市场营销</t>
-        </is>
-      </c>
-      <c r="D8" s="0" t="inlineStr">
-        <is>
-          <t>广告接入技术支持工程师
-30k 在家 办公</t>
-        </is>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F8" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H8" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="I8" s="0" t="inlineStr">
-        <is>
-          <t>岗位职责：
-1.  深度支持接入： 指导站长在 WP (Hooks/Footer/Plugin)、AppleCMS 、Z-Blog 等各类复杂 CMS 环境下完成广告代码的**高性能植入**。
-2.  技术故障攻坚： 独立定位并排查 JS 报错、CSS 布局塌陷、Iframe 权限限制**及 **CDN 缓存同步**等接入难题。
-3.  **环境适配优化： 针对不同浏览器内核及广告拦截器（ AdBlocker ），提供**代码混淆、动态注入或域名反代**等技术绕过与兼容性建议。  Ym9iY3J0Z3ZzQGdtYWlsLmNvbQ==</t>
-        </is>
-      </c>
-      <c r="J8" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K8" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L8" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1202125#reply0</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1905,12 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>远程工作</t>
+          <t>后端开发</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>[远程] 招聘航司逆向安全工程师</t>
+          <t>寻远程运维/后端工程师， AI 算力服务方向，长期合作</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -1938,38 +1930,34 @@
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t>岗位职责：
-针对航司官网及移动端应用的通信协议进行安全审计与逆向分析
-研究主流航司的请求签名算法（如行业常见的 AK 系列、RE 系列参数体系及其衍生变种）
-持续跟踪航司安全策略迭代，维护技术方案的可用性
-与业务开发团队协作，定义数据接口规范</t>
+          <t>详见原帖</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t>10K/月起（税前）</t>
+          <t>面议</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L9" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1202059#reply6</t>
+          <t>微信: HongKong_China-</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1201439#reply0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>海外公司</t>
+          <t>海外游戏公司招</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
@@ -1979,12 +1967,12 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>后端开发</t>
+          <t>运营</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>[远程长期+合伙人] Go 后端 + WebRTC 技术负责人</t>
+          <t>海外游戏公司招聘 2 个职位-渗透测试-安全运营</t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr">
@@ -2004,20 +1992,13 @@
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t>岗位职责：
-我们有一套成熟的移动设备管理产品（ MDM ），已上线运营，
-目前用户量稳定增长，现有技术架构面临性能和维护瓶颈，
-决定进行全面技术升级重构。
-━━━━━━━━━━━━━━━━━━━━━━
-当前架构 → 目标架构
-服务端：PHP + Node.js  →  Go （统一单服务）
-通信层：纯 WebSocket  →  WebRTC + WebSocket 双协议
-VB.NET</t>
+          <t>岗位职责：安全监控与日志分析；• 负责 Splunk 等 SIEM 平台的日常运营和优化，设计并实现安全日志收集、存储、分析策略；；• 监控各类安全日志，识别异常行为，分析安全事件，提升检测能力；；• 创建并维护 SIEM 规则、仪表盘、告警策略，提高威胁检测效率。；应急响应与事件处置
+任职要求：熟悉 Splunk 等 SIEM 平台的部署、管理、规则编写及告警优化，有 Splunk ES （ Enterprise Security ）经验者优先；；具备安全事件分析与应急响应能力，熟悉 APT 攻击分析、恶意代码分析、网络入侵溯源等技术；；熟悉主流云计算平台的安全架构、日志分析和防护机制；熟悉常见安全框架和标准，如 MITRE ATT&amp;CK 、CIS 、NIST 、ISO 27001；具备一定的编程能力（ Python 、java 、Bash 等），能够开发安全自动化工具；</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">
@@ -2027,19 +2008,19 @@
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t>Telegram: reSQL</t>
-        </is>
-      </c>
-      <c r="L10" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1202024#reply6</t>
+          <t>星球同学 私Junes内推</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1200917#reply1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>Atria 是一家基于人工智能的广告创意管理平台</t>
+          <t>海外公司</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
@@ -2049,12 +2030,12 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>前端开发</t>
+          <t>AI/算法</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>[远程][外企] Atria 招聘 测试兼职/前端/产品</t>
+          <t>AI 创业团队找一位运维开发工程师！</t>
         </is>
       </c>
       <c r="E11" s="0" t="inlineStr">
@@ -2074,20 +2055,13 @@
       </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="I11" s="0" t="inlineStr">
         <is>
-          <t>岗位职责：
-Atria 是一家基于人工智能的广告创意管理平台，致力于帮助营销人员更高效地创作高表现广告，从而提升 Meta 和 TikTok 等平台的广告投放效果。我们服务于众多知名公司，包括 Perplexity, ClickUp, Beehiiv, True Classic 。
-公司已完成天使轮融资，创立三年多，目前公司收月入远大于每月各方面支出，营收还在不断高速增长中。
-工作地点： 远程办公
-研发团队都是中国人，日常开发用中文交流即可。
-全远程工作，工作地点无要求，最好在亚太时区。
-研发 10 人，产品设计 3 人，团队成员主要来自腾讯、亚马逊和微软等国内外知名大厂。
-积极拥抱 AI ，公司给研发产品设计团队都提供 Codex 和 Claude Code 账号。
-1. 兼职测试工程师（每周≥3 天）</t>
+          <t>岗位职责：搭建并维护 CI/CD 流水线，基于 Github Action 、Gitlab CI/CD 等工具实现代码自动构建、测试与部署；；负责 Docker 镜像构建与优化，制定镜像规范，减少镜像体积，提升构建效率；；管理和维护 Kubernetes 集群（包括部署、扩缩容、监控告警、故障排查），保障集群稳定运行；；推进微服务架构下的容器化部署方案，制定服务发现、配置管理、灰度发布等策略；；负责多 Agent 系统的部署、编排与运维，确保各 Agent 服务的高可用与可观测性；
+任职要求：熟悉使用常见的代码仓库和配套组件，包括但不限于 Github 、Github Action 、Gitlab 、Gitlab Runner 等，能独立完成流水线搭建与维护；；精通 DevOps 理念与实践，掌握 Docker 镜像优化（多阶段构建、层缓存策略等），熟练进行 K8s 集群管理与容器化部署；；熟悉微服务架构设计与治理，具备多 Agent 系统的管理、部署与运维经验。</t>
         </is>
       </c>
       <c r="J11" s="0" t="inlineStr">
@@ -2102,7 +2076,7 @@
       </c>
       <c r="L11" s="0" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1201856#reply7</t>
+          <t>https://www.v2ex.com/t/1200637#reply5</t>
         </is>
       </c>
     </row>
@@ -2119,12 +2093,12 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>远程工作</t>
+          <t>全栈开发</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>一直想做的远程工作集合网站，上线了</t>
+          <t>[招聘-接受远程] AGI 全栈工程师（AI Agent / IoT-RTC）</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
@@ -2149,20 +2123,13 @@
       </c>
       <c r="I12" s="0" t="inlineStr">
         <is>
-          <t>岗位职责：
-前段时间找远程工作，横跳在各个平台之间，
-领英、indeed 、Glassdoor
-、各个公司的
-Careers 页面
-，烦不胜烦。
-于是乎，整一个爬虫，汇集各个平台的
-，把工作标题和内容也都
-翻译成了中文</t>
+          <t>岗位职责：我们要做的，是把 AI 真正接入 IoT 世界：让摄像头能理解画面、让设备能听懂指令、让海量视频数据产生业务价值，是客户真正在用、愿意付费的产品功能。；- 将视觉 AI （人形检测、包裹识别、异常行为分析）、LLM （视频摘要、指令交互）、语音 AI 集成进 Ti RTC 平台，打造有付费价值的 AI 增值服务；- 独立负责 AI 功能全链路工程化：模型/API 选型、接口封装、异步调度、结果缓存、效果监控，对生产稳定性负责；- 主导 AI 场景技术评估，判断哪些场景值得做、评估精度/延迟/成本的平衡点，不做无效集成；- 将 AI 工具用到极致，同时推动 AI 在团队研发流程中的深度落地
+任职要求：- 出色的代码能力，语言不限（ Python / Go 均可）；- 有将 AI 能力集成进真实产品的工程经验（有真实用户在使用、效果可度量，不是内部工具或 Demo ）；- 能独立完成从需求评估、技术选型到生产上线的完整链路，对效果和稳定性负责；- 本人就是 AI 工具的重度用户：日常使用 Cursor / Claude Code 等工具开发，能清晰描述 AI 如何改变了你的</t>
         </is>
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t>面议</t>
+          <t>20K–45K ，根据能力面议</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
@@ -2172,14 +2139,14 @@
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1201311#reply13</t>
+          <t>https://www.v2ex.com/t/1200788#reply0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t>远程岗位</t>
+          <t>海外公司</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
@@ -2189,12 +2156,12 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>后端开发</t>
+          <t>区块链</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>远程岗位：高级产品经理（AI 方向），广告接入技术支持工程师，远程 QA 测试工程师， PHP ， web， Flutter</t>
+          <t>HR 直招：🔥区块链高级安全工程师 - 远程 remote 办公</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
@@ -2219,46 +2186,30 @@
       </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t>岗位职责：
-1. 负责 AI 相关产品的规划、设计与迭代。
-2. 结合公司业务方向，挖掘 AI 在业务场景中的落地机会。
-3. 输出高质量 PRD 、流程图、原型图及需求说明文档。
-4. 协同研发、设计、运营团队推进项目落地，确保版本按时高质量交付。
-5. 跟踪行业动态、竞争产品与技术趋势，持续提出产品优化与创新方案。
-6. 对产品上线后的使用数据、转化数据、用户反馈进行分析，持续优化产品体验和业务结果。
-7. 参与 AI 工具、AI 工作流、AI 业务能力在公司内部的应用推进。
--------
-任职要求：
-1.  前端基础： 扎实的 HTML/JavaScript 功底，能熟练使用 Chrome DevTools 进行断点调试与网络层请求分析。
-2.  CMS 经验： 深度熟悉 WordPress 钩子机制 (Hooks)**、AppleCMS 模板逻辑或类似内容的二次开发。
-3.  **安全模型： 熟悉浏览器安全模型（**CORS 、CSP 、Sandbox**）及常见的广告拦截（ AdBlock ）对抗原理。
-4.  专业加分： 有 Ad Network (广告联盟) 实际接入经验，或对 HTTP 协议、CDN 调优有深入理解。
-5.  沟通能力： 具备“技术+服务”意识，能将复杂技术问题转化为易于站长理解的可执行方案。
-四、 岗位价值说明 (Value Proposition)
-* 转化率保障： 该岗位直接负责将“意向站长”转化为“活跃投放点”，是业务转化漏斗中的核心节点。
-* 技术壁垒： 通过沉淀针对各主流 CMS 的自动化接入方案，构建联盟在技术服务侧的竞争护城河。</t>
+          <t>岗位职责：- 全链路安全审计： 负责对区块链业务全链路进行安全评估与渗透测试。；- 智能合约安全： 负责智能合约的代码安全审计。；- 基础与云安全运营： 参与云端服务及终端环境的渗透测试与安全加固。
+任职要求：- 本科及以上学历优先，计算机、信息安全或网络安全等相关专业更佳。；- 具备 3-5 年相关工作经验，尤其是在信息安全或区块链安全相关领域具有实战经验。；- 熟悉区块链底层系统架构及智能合约相关知识；熟悉 Web3 领域常见的攻击手法及对应的防御策略（熟练使用 Slither 、Mythril 、Echidna 等合约审计与测试工具，熟悉 Foundry / Hardhat 等环境）。；- 具备扎实的网络安全功底，熟练掌握渗透测试、漏洞挖掘、网络流量分析及恶意代码分析等常规安全技能（熟练掌握 Burp Suite 、Nmap 、Wireshark 、IDA Pro 等行业主流攻防与分析工具）。；- 有大型安全项目的参与或落地经验，具备独立排查并解决实际安全问题的能力；在云环境的安全攻防方面具备一定的实操经验。</t>
         </is>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>50k+</t>
+          <t>面议</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t>Telegram: Skyewen20251</t>
+          <t>星球同学 私Junes内推</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1201527#reply1</t>
+          <t>https://www.v2ex.com/t/1200785#reply0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t>外企招</t>
+          <t>海外公司</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
@@ -2268,12 +2219,12 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>后端开发</t>
+          <t>AI/算法</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>外企招聘数据工程师 20-50w/year (接受后端转)-full remote</t>
+          <t>[远程工作] Web3 交易所招 AI 落地工程师啦～～薪资待遇可谈</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
@@ -2298,15 +2249,8 @@
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t>岗位职责：
-这是我之前发的招聘：
-https://v2ex.com/t/1194552?p=1#reply9
-全栈已经招到了。
-之前投给我的数据工程师的简历，大部分都被安排面试了。
-目前数据工程师的 HC 是最多的。
-另外，我们也接受经验丰富的后端工程师，处理过复杂的系统的，愿意转做数据工程师的，也可以。
-再强调一下，英语口语要可以工作，你的同事大部分是印度人，泰国人。
-公司简介，福利等见我之前的帖子，总体来说都还挺不错的。</t>
+          <t>岗位职责：APP 产品 AI 化（提升交易活跃度与用户粘性）；智能交易助手： 负责开发 AI 辅助交易功能（如基于自然语言的指令下单、智能止盈止损策略建议）。；行情辅助决策： 利用大模型（ LLM ）集成多源信息（新闻、推特情绪、链上数据），为用户提供实时研报、代币分析及风险预警。；个性化推荐： 基于用户交易行为，利用机器学习模型进行个性化的币种推荐、策略跟单推荐及投教内容分发。；客服机器人 2.0： 将传统的规则引擎客服升级为基于 RAG （检索增强生成）的 AI 客服，处理 80% 以上的复杂业务咨询。
+任职要求：教育背景（ Education ）；名校毕业，技术专业；工作经验（ Experience ）；3-5 年加密货币交易所、量化交易或金融科技（ Fintech ）产品经验，对交易所业务模型（现货、合约、流动性）有深刻理解。学习和工作经历能够证明对 LLM 和 ai agent 有足够的了解，最近经历涉及 workflow 的智能化改造并且有成功经验；能力与技能（ Skills &amp; Competencies ）</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
@@ -2321,14 +2265,14 @@
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1198745#reply4</t>
+          <t>https://www.v2ex.com/t/1200784#reply0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t>远程岗位</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
@@ -2338,12 +2282,12 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>后端开发</t>
+          <t>AI/算法</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>远程岗位：高级产品经理（AI 方向），广告接入技术支持工程师，远程 QA 测试工程师， PHP ， web， Flutter</t>
+          <t>远程大数据开发，推荐算法工程师，有兴趣可以聊聊</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
@@ -2368,23 +2312,22 @@
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t>岗位职责：1. 负责 AI 相关产品的规划、设计与迭代。；2. 结合公司业务方向，挖掘 AI 在业务场景中的落地机会。；3. 输出高质量 PRD 、流程图、原型图及需求说明文档。；4. 协同研发、设计、运营团队推进项目落地，确保版本按时高质量交付。；5. 跟踪行业动态、竞争产品与技术趋势，持续提出产品优化与创新方案。
-任职要求：1.  前端基础： 扎实的 HTML/JavaScript 功底，能熟练使用 Chrome DevTools 进行断点调试与网络层请求分析。；2.  CMS 经验： 深度熟悉 WordPress 钩子机制 (Hooks)**、AppleCMS 模板逻辑或类似内容的二次开发。；3.  **安全模型： 熟悉浏览器安全模型（**CORS 、CSP 、Sandbox**）及常见的广告拦截（ AdBlock ）对抗原理。；4.  专业加分： 有 Ad Network (广告联盟) 实际接入经验，或对 HTTP 协议、CDN 调优有深入理解。；5.  沟通能力： 具备“技术+服务”意识，能将复杂技术问题转化为易于站长理解的可执行方案。</t>
+          <t>详见原帖</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t>50k+</t>
+          <t>25k-45k</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t>Skyewen20251</t>
+          <t>星球同学 私Junes内推</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1201527#reply1</t>
+          <t>https://www.v2ex.com/t/1200673#reply0</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2349,7 @@
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>寻远程运维/后端工程师， AI 算力服务方向，长期合作</t>
+          <t>golang 后端兼职—跨境电商 SaaS+AI</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
@@ -2431,29 +2374,30 @@
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t>详见原帖</t>
+          <t>岗位职责：岗位：Golang 后端工程师；*工作地点：深圳坂田；薪资：固定薪资+ 期权（面议）；团队规模：10 人创业团队，产品/技术/市场/运营齐备；参与后端架构设计与核心模块开发，保证 API 高可用、高并发。</t>
         </is>
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t>面议</t>
+          <t>固定薪资+ 期权（面议）</t>
         </is>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t>微信: HongKong_China-</t>
-        </is>
-      </c>
-      <c r="L16" s="13" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1201439#reply0</t>
+          <t>微信: godhaveajoke
+reSQL</t>
+        </is>
+      </c>
+      <c r="L16" s="0" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1200518#reply7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t>海外游戏公司招</t>
+          <t>海外公司</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
@@ -2463,12 +2407,12 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>运营</t>
+          <t>UI/UX设计</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>海外游戏公司招聘 2 个职位-渗透测试-安全运营</t>
+          <t>[远程] 招聘 中高级 UI/UX 设计师！</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
@@ -2493,8 +2437,8 @@
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t>岗位职责：安全监控与日志分析；• 负责 Splunk 等 SIEM 平台的日常运营和优化，设计并实现安全日志收集、存储、分析策略；；• 监控各类安全日志，识别异常行为，分析安全事件，提升检测能力；；• 创建并维护 SIEM 规则、仪表盘、告警策略，提高威胁检测效率。；应急响应与事件处置
-任职要求：熟悉 Splunk 等 SIEM 平台的部署、管理、规则编写及告警优化，有 Splunk ES （ Enterprise Security ）经验者优先；；具备安全事件分析与应急响应能力，熟悉 APT 攻击分析、恶意代码分析、网络入侵溯源等技术；；熟悉主流云计算平台的安全架构、日志分析和防护机制；熟悉常见安全框架和标准，如 MITRE ATT&amp;CK 、CIS 、NIST 、ISO 27001；具备一定的编程能力（ Python 、java 、Bash 等），能够开发安全自动化工具；</t>
+          <t>岗位职责：负责相机 App 整体视觉风格定位，完成首页、拍摄页、相册页、设置页等所有静态页面的 UI 设计，确保视觉效果贴合相机产品定位，兼具美观性与实用性。；主导相机 App 用户体验流程设计，梳理拍摄、预览、修图、分享等核心操作逻辑，完成交互原型设计，优化用户操作路径，提升产品易用性与流畅度。；Material Design 设计规范；，把控界面布局、色彩搭配、图标设计、字体排版等基础设计细节，保证产品设计的统一性与规范性。；负责相机 App 关键场景动效设计，包括拍摄快门动效、滤镜切换动效、页面转场动效、操作反馈动效等，通过优质动效提升产品质感与用户交互体验。
+任职要求：大专及以上学历，设计相关专业（视觉传达、数字媒体、工业设计等），1-3 年及以上 UI/UX 设计相关工作经验，有相机类、摄影类 App 设计经验者优先。；精通 Material Design 设计规范；，熟练掌握 UI 设计基础规范，对界面布局、色彩系统、组件设计、交互逻辑有深刻理解，能独立完成符合规范的设计作品。；具备扎实的静态页面设计能力，熟练使用 Figma 、Sketch 、PS 、AI 等设计工具，能高效输出高质量视觉设计稿，审美在线，擅长简约、质感类设计风格。；掌握动效设计技能，熟悉 AE 、Principle 等动效设计工具，能独立完成流畅、贴合产品场景的动效设计，懂基础交互逻辑与动效原理。</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
@@ -2507,9 +2451,9 @@
           <t>星球同学 私Junes内推</t>
         </is>
       </c>
-      <c r="L17" s="13" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1200917#reply1</t>
+      <c r="L17" s="0" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1200541#reply0</t>
         </is>
       </c>
     </row>
@@ -2526,12 +2470,12 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>远程工作</t>
+          <t>UI/UX设计</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>远程工作网站开放</t>
+          <t>Unlimit Pro is hiring Talent Acquisition Manager</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
@@ -2571,7 +2515,7 @@
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1200863#reply10</t>
+          <t>https://www.v2ex.com/t/1200738#reply0</t>
         </is>
       </c>
     </row>
@@ -2588,12 +2532,12 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>AI/算法</t>
+          <t>后端开发</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>AI 创业团队找一位运维开发工程师！</t>
+          <t>招聘多模态搜索后端工程师， founding engineer</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
@@ -2618,8 +2562,7 @@
       </c>
       <c r="I19" s="0" t="inlineStr">
         <is>
-          <t>岗位职责：搭建并维护 CI/CD 流水线，基于 Github Action 、Gitlab CI/CD 等工具实现代码自动构建、测试与部署；；负责 Docker 镜像构建与优化，制定镜像规范，减少镜像体积，提升构建效率；；管理和维护 Kubernetes 集群（包括部署、扩缩容、监控告警、故障排查），保障集群稳定运行；；推进微服务架构下的容器化部署方案，制定服务发现、配置管理、灰度发布等策略；；负责多 Agent 系统的部署、编排与运维，确保各 Agent 服务的高可用与可观测性；
-任职要求：熟悉使用常见的代码仓库和配套组件，包括但不限于 Github 、Github Action 、Gitlab 、Gitlab Runner 等，能独立完成流水线搭建与维护；；精通 DevOps 理念与实践，掌握 Docker 镜像优化（多阶段构建、层缓存策略等），熟练进行 K8s 集群管理与容器化部署；；熟悉微服务架构设计与治理，具备多 Agent 系统的管理、部署与运维经验。</t>
+          <t>详见原帖</t>
         </is>
       </c>
       <c r="J19" s="0" t="inlineStr">
@@ -2634,7 +2577,7 @@
       </c>
       <c r="L19" s="0" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1200637#reply5</t>
+          <t>https://www.v2ex.com/t/1200228#reply2</t>
         </is>
       </c>
     </row>
@@ -2651,12 +2594,12 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>全栈开发</t>
+          <t>AI/算法</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>[招聘-接受远程] AGI 全栈工程师（AI Agent / IoT-RTC）</t>
+          <t>招两个远程工作，熟练基于开源大模型文本训练，视频训练的岗位</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
@@ -2681,13 +2624,12 @@
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t>岗位职责：我们要做的，是把 AI 真正接入 IoT 世界：让摄像头能理解画面、让设备能听懂指令、让海量视频数据产生业务价值，是客户真正在用、愿意付费的产品功能。；- 将视觉 AI （人形检测、包裹识别、异常行为分析）、LLM （视频摘要、指令交互）、语音 AI 集成进 Ti RTC 平台，打造有付费价值的 AI 增值服务；- 独立负责 AI 功能全链路工程化：模型/API 选型、接口封装、异步调度、结果缓存、效果监控，对生产稳定性负责；- 主导 AI 场景技术评估，判断哪些场景值得做、评估精度/延迟/成本的平衡点，不做无效集成；- 将 AI 工具用到极致，同时推动 AI 在团队研发流程中的深度落地
-任职要求：- 出色的代码能力，语言不限（ Python / Go 均可）；- 有将 AI 能力集成进真实产品的工程经验（有真实用户在使用、效果可度量，不是内部工具或 Demo ）；- 能独立完成从需求评估、技术选型到生产上线的完整链路，对效果和稳定性负责；- 本人就是 AI 工具的重度用户：日常使用 Cursor / Claude Code 等工具开发，能清晰描述 AI 如何改变了你的</t>
+          <t>详见原帖</t>
         </is>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t>20K–45K ，根据能力面议</t>
+          <t>面议</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
@@ -2697,14 +2639,14 @@
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1200788#reply0</t>
+          <t>https://www.v2ex.com/t/1200008#reply4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t>海外公司</t>
+          <t>BitFit</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
@@ -2714,12 +2656,12 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>区块链</t>
+          <t>远程工作</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>HR 直招：🔥区块链高级安全工程师 - 远程 remote 办公</t>
+          <t>BitFit 招聘（远程）</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
@@ -2744,8 +2686,7 @@
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t>岗位职责：- 全链路安全审计： 负责对区块链业务全链路进行安全评估与渗透测试。；- 智能合约安全： 负责智能合约的代码安全审计。；- 基础与云安全运营： 参与云端服务及终端环境的渗透测试与安全加固。
-任职要求：- 本科及以上学历优先，计算机、信息安全或网络安全等相关专业更佳。；- 具备 3-5 年相关工作经验，尤其是在信息安全或区块链安全相关领域具有实战经验。；- 熟悉区块链底层系统架构及智能合约相关知识；熟悉 Web3 领域常见的攻击手法及对应的防御策略（熟练使用 Slither 、Mythril 、Echidna 等合约审计与测试工具，熟悉 Foundry / Hardhat 等环境）。；- 具备扎实的网络安全功底，熟练掌握渗透测试、漏洞挖掘、网络流量分析及恶意代码分析等常规安全技能（熟练掌握 Burp Suite 、Nmap 、Wireshark 、IDA Pro 等行业主流攻防与分析工具）。；- 有大型安全项目的参与或落地经验，具备独立排查并解决实际安全问题的能力；在云环境的安全攻防方面具备一定的实操经验。</t>
+          <t>岗位职责：·  负责 MPC 钱包产品的整体规划，进行深入的市场、竞品及用户研究，定义产品定位、核心功能和长期发展路线图。；·  主导产品从概念、设计、开发、测试到上线、运营的全生命周期管理，撰写清晰的产品需求文档（ PRD ）和原型，并高效推动项目执行。；·  作为项目核心枢纽，高效协调研发、设计、市场、运营及安全团队，确保信息对齐、目标一致，并对最终的产品结果和用户体验负责。；·  建立并监控核心产品数据指标，通过用户反馈、行为数据及市场变化，持续推动产品优化与快速迭代。；·  紧密跟踪区块链、加密货币、钱包安全及 Web3 行业动态，将前沿趋势转化为产品机遇。</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
@@ -2760,7 +2701,7 @@
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1200785#reply0</t>
+          <t>https://www.v2ex.com/t/1200330#reply0</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2718,12 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>AI/算法</t>
+          <t>产品经理</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>[远程工作] Web3 交易所招 AI 落地工程师啦～～薪资待遇可谈</t>
+          <t>[远程][外企] Atria 招聘 多个研发岗位和产品设计师</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
@@ -2807,8 +2748,7 @@
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t>岗位职责：APP 产品 AI 化（提升交易活跃度与用户粘性）；智能交易助手： 负责开发 AI 辅助交易功能（如基于自然语言的指令下单、智能止盈止损策略建议）。；行情辅助决策： 利用大模型（ LLM ）集成多源信息（新闻、推特情绪、链上数据），为用户提供实时研报、代币分析及风险预警。；个性化推荐： 基于用户交易行为，利用机器学习模型进行个性化的币种推荐、策略跟单推荐及投教内容分发。；客服机器人 2.0： 将传统的规则引擎客服升级为基于 RAG （检索增强生成）的 AI 客服，处理 80% 以上的复杂业务咨询。
-任职要求：教育背景（ Education ）；名校毕业，技术专业；工作经验（ Experience ）；3-5 年加密货币交易所、量化交易或金融科技（ Fintech ）产品经验，对交易所业务模型（现货、合约、流动性）有深刻理解。学习和工作经历能够证明对 LLM 和 ai agent 有足够的了解，最近经历涉及 workflow 的智能化改造并且有成功经验；能力与技能（ Skills &amp; Competencies ）</t>
+          <t>详见原帖</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
@@ -2823,14 +2763,14 @@
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1200784#reply0</t>
+          <t>https://www.v2ex.com/t/1199798#reply9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>海外公司</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
@@ -2845,7 +2785,7 @@
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>远程大数据开发，推荐算法工程师，有兴趣可以聊聊</t>
+          <t>[全职远程工作 ] AI 翻译/个人知识助手应用 iOS/Android 开发（限 3 ～ 5 年工作经验）</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
@@ -2875,7 +2815,7 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t>25k-45k</t>
+          <t>面议</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
@@ -2885,7 +2825,7 @@
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1200673#reply0</t>
+          <t>https://www.v2ex.com/t/1199498#reply3</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2842,12 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>后端开发</t>
+          <t>前端开发</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t>golang 后端兼职—跨境电商 SaaS+AI</t>
+          <t>[全职远程] AI-Native Java /React 全栈工程师</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
@@ -2932,30 +2872,31 @@
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t>岗位职责：岗位：Golang 后端工程师；*工作地点：深圳坂田；薪资：固定薪资+ 期权（面议）；团队规模：10 人创业团队，产品/技术/市场/运营齐备；参与后端架构设计与核心模块开发，保证 API 高可用、高并发。</t>
+          <t>岗位职责：参与该产品 V2.0 的需求分析、方案设计与研发交付，使用 Ai-native 的方式，负责从前端到后端的端到端实现（接口、数据模型、页面、联调与上线）。；基于 V1.0 的项目，使用 AI 编程工具，开发与维护核心业务模块：元数据采集/管理、数据发现与检索、服务请求与审批工作流、订阅/成本/授权（ Inventory ）管理等功能。；设计并实现高质量的 API 与领域模型，确保可维护性、可扩展性与可测试性（遵循 DDD / SOLID 等原则）。；使用并沉淀 AI 辅助研发与“Vibe Coding”工作流：用 AI 提升效率，同时通过测试与工程规范保证质量。
+任职要求：沟通主动积极，有良好的职业素养、工作习惯和团队意识；能独立推进任务闭环。；良好的英语读写能力（能阅读英文技术文档、进行基本技术沟通）。；4 年以上开发经验，具备全栈交付能力（能同时覆盖后端与前端关键链路），对“工程化交付”有较强意识。；AI-Native / Vibe Coding；熟练使用 AI 编程工具（如 Codex ，Claude Code ）完成：</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t>固定薪资+ 期权（面议）</t>
+          <t>15-25k</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t>微信: godhaveajoke
+          <t>微信: base64
 reSQL</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1200518#reply7</t>
+          <t>https://www.v2ex.com/t/1199537#reply1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t>海外公司</t>
+          <t>外企招</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
@@ -2965,12 +2906,12 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>UI/UX设计</t>
+          <t>后端开发</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t>[远程] 招聘 中高级 UI/UX 设计师！</t>
+          <t>外企招聘数据工程师 20-50w/year (接受后端转)-full remote</t>
         </is>
       </c>
       <c r="E25" s="0" t="inlineStr">
@@ -2995,8 +2936,7 @@
       </c>
       <c r="I25" s="0" t="inlineStr">
         <is>
-          <t>岗位职责：负责相机 App 整体视觉风格定位，完成首页、拍摄页、相册页、设置页等所有静态页面的 UI 设计，确保视觉效果贴合相机产品定位，兼具美观性与实用性。；主导相机 App 用户体验流程设计，梳理拍摄、预览、修图、分享等核心操作逻辑，完成交互原型设计，优化用户操作路径，提升产品易用性与流畅度。；Material Design 设计规范；，把控界面布局、色彩搭配、图标设计、字体排版等基础设计细节，保证产品设计的统一性与规范性。；负责相机 App 关键场景动效设计，包括拍摄快门动效、滤镜切换动效、页面转场动效、操作反馈动效等，通过优质动效提升产品质感与用户交互体验。
-任职要求：大专及以上学历，设计相关专业（视觉传达、数字媒体、工业设计等），1-3 年及以上 UI/UX 设计相关工作经验，有相机类、摄影类 App 设计经验者优先。；精通 Material Design 设计规范；，熟练掌握 UI 设计基础规范，对界面布局、色彩系统、组件设计、交互逻辑有深刻理解，能独立完成符合规范的设计作品。；具备扎实的静态页面设计能力，熟练使用 Figma 、Sketch 、PS 、AI 等设计工具，能高效输出高质量视觉设计稿，审美在线，擅长简约、质感类设计风格。；掌握动效设计技能，熟悉 AE 、Principle 等动效设计工具，能独立完成流畅、贴合产品场景的动效设计，懂基础交互逻辑与动效原理。</t>
+          <t>详见原帖</t>
         </is>
       </c>
       <c r="J25" s="0" t="inlineStr">
@@ -3010,504 +2950,6 @@
         </is>
       </c>
       <c r="L25" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1200541#reply0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0" t="inlineStr">
-        <is>
-          <t>海外公司</t>
-        </is>
-      </c>
-      <c r="B26" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C26" s="0" t="inlineStr">
-        <is>
-          <t>UI/UX设计</t>
-        </is>
-      </c>
-      <c r="D26" s="0" t="inlineStr">
-        <is>
-          <t>Unlimit Pro is hiring Talent Acquisition Manager</t>
-        </is>
-      </c>
-      <c r="E26" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F26" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G26" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H26" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I26" s="0" t="inlineStr">
-        <is>
-          <t>详见原帖</t>
-        </is>
-      </c>
-      <c r="J26" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K26" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L26" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1200738#reply0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="0" t="inlineStr">
-        <is>
-          <t>海外公司</t>
-        </is>
-      </c>
-      <c r="B27" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C27" s="0" t="inlineStr">
-        <is>
-          <t>后端开发</t>
-        </is>
-      </c>
-      <c r="D27" s="0" t="inlineStr">
-        <is>
-          <t>招聘多模态搜索后端工程师， founding engineer</t>
-        </is>
-      </c>
-      <c r="E27" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F27" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G27" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H27" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I27" s="0" t="inlineStr">
-        <is>
-          <t>详见原帖</t>
-        </is>
-      </c>
-      <c r="J27" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K27" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L27" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1200228#reply2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="0" t="inlineStr">
-        <is>
-          <t>海外公司</t>
-        </is>
-      </c>
-      <c r="B28" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C28" s="0" t="inlineStr">
-        <is>
-          <t>AI/算法</t>
-        </is>
-      </c>
-      <c r="D28" s="0" t="inlineStr">
-        <is>
-          <t>招两个远程工作，熟练基于开源大模型文本训练，视频训练的岗位</t>
-        </is>
-      </c>
-      <c r="E28" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F28" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G28" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H28" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I28" s="0" t="inlineStr">
-        <is>
-          <t>详见原帖</t>
-        </is>
-      </c>
-      <c r="J28" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K28" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L28" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1200008#reply4</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="inlineStr">
-        <is>
-          <t>BitFit</t>
-        </is>
-      </c>
-      <c r="B29" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C29" s="0" t="inlineStr">
-        <is>
-          <t>远程工作</t>
-        </is>
-      </c>
-      <c r="D29" s="0" t="inlineStr">
-        <is>
-          <t>BitFit 招聘（远程）</t>
-        </is>
-      </c>
-      <c r="E29" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F29" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G29" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H29" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I29" s="0" t="inlineStr">
-        <is>
-          <t>岗位职责：·  负责 MPC 钱包产品的整体规划，进行深入的市场、竞品及用户研究，定义产品定位、核心功能和长期发展路线图。；·  主导产品从概念、设计、开发、测试到上线、运营的全生命周期管理，撰写清晰的产品需求文档（ PRD ）和原型，并高效推动项目执行。；·  作为项目核心枢纽，高效协调研发、设计、市场、运营及安全团队，确保信息对齐、目标一致，并对最终的产品结果和用户体验负责。；·  建立并监控核心产品数据指标，通过用户反馈、行为数据及市场变化，持续推动产品优化与快速迭代。；·  紧密跟踪区块链、加密货币、钱包安全及 Web3 行业动态，将前沿趋势转化为产品机遇。</t>
-        </is>
-      </c>
-      <c r="J29" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K29" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L29" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1200330#reply0</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="inlineStr">
-        <is>
-          <t>海外公司</t>
-        </is>
-      </c>
-      <c r="B30" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C30" s="0" t="inlineStr">
-        <is>
-          <t>产品经理</t>
-        </is>
-      </c>
-      <c r="D30" s="0" t="inlineStr">
-        <is>
-          <t>[远程][外企] Atria 招聘 多个研发岗位和产品设计师</t>
-        </is>
-      </c>
-      <c r="E30" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F30" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G30" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H30" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I30" s="0" t="inlineStr">
-        <is>
-          <t>详见原帖</t>
-        </is>
-      </c>
-      <c r="J30" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K30" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L30" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1199798#reply9</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="inlineStr">
-        <is>
-          <t>海外公司</t>
-        </is>
-      </c>
-      <c r="B31" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C31" s="0" t="inlineStr">
-        <is>
-          <t>AI/算法</t>
-        </is>
-      </c>
-      <c r="D31" s="0" t="inlineStr">
-        <is>
-          <t>[全职远程工作 ] AI 翻译/个人知识助手应用 iOS/Android 开发（限 3 ～ 5 年工作经验）</t>
-        </is>
-      </c>
-      <c r="E31" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F31" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G31" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H31" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I31" s="0" t="inlineStr">
-        <is>
-          <t>详见原帖</t>
-        </is>
-      </c>
-      <c r="J31" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K31" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L31" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1199498#reply3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="inlineStr">
-        <is>
-          <t>海外公司</t>
-        </is>
-      </c>
-      <c r="B32" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C32" s="0" t="inlineStr">
-        <is>
-          <t>前端开发</t>
-        </is>
-      </c>
-      <c r="D32" s="0" t="inlineStr">
-        <is>
-          <t>[全职远程] AI-Native Java /React 全栈工程师</t>
-        </is>
-      </c>
-      <c r="E32" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F32" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G32" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H32" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I32" s="0" t="inlineStr">
-        <is>
-          <t>岗位职责：参与该产品 V2.0 的需求分析、方案设计与研发交付，使用 Ai-native 的方式，负责从前端到后端的端到端实现（接口、数据模型、页面、联调与上线）。；基于 V1.0 的项目，使用 AI 编程工具，开发与维护核心业务模块：元数据采集/管理、数据发现与检索、服务请求与审批工作流、订阅/成本/授权（ Inventory ）管理等功能。；设计并实现高质量的 API 与领域模型，确保可维护性、可扩展性与可测试性（遵循 DDD / SOLID 等原则）。；使用并沉淀 AI 辅助研发与“Vibe Coding”工作流：用 AI 提升效率，同时通过测试与工程规范保证质量。
-任职要求：沟通主动积极，有良好的职业素养、工作习惯和团队意识；能独立推进任务闭环。；良好的英语读写能力（能阅读英文技术文档、进行基本技术沟通）。；4 年以上开发经验，具备全栈交付能力（能同时覆盖后端与前端关键链路），对“工程化交付”有较强意识。；AI-Native / Vibe Coding；熟练使用 AI 编程工具（如 Codex ，Claude Code ）完成：</t>
-        </is>
-      </c>
-      <c r="J32" s="0" t="inlineStr">
-        <is>
-          <t>15-25k</t>
-        </is>
-      </c>
-      <c r="K32" s="0" t="inlineStr">
-        <is>
-          <t>微信: base64
-reSQL</t>
-        </is>
-      </c>
-      <c r="L32" s="0" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1199537#reply1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="inlineStr">
-        <is>
-          <t>外企招</t>
-        </is>
-      </c>
-      <c r="B33" s="0" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="C33" s="0" t="inlineStr">
-        <is>
-          <t>后端开发</t>
-        </is>
-      </c>
-      <c r="D33" s="0" t="inlineStr">
-        <is>
-          <t>外企招聘数据工程师 20-50w/year (接受后端转)-full remote</t>
-        </is>
-      </c>
-      <c r="E33" s="0" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F33" s="0" t="inlineStr">
-        <is>
-          <t>内推岗</t>
-        </is>
-      </c>
-      <c r="G33" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="H33" s="0" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I33" s="0" t="inlineStr">
-        <is>
-          <t>详见原帖</t>
-        </is>
-      </c>
-      <c r="J33" s="0" t="inlineStr">
-        <is>
-          <t>面议</t>
-        </is>
-      </c>
-      <c r="K33" s="0" t="inlineStr">
-        <is>
-          <t>星球同学 私Junes内推</t>
-        </is>
-      </c>
-      <c r="L33" s="0" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1198745#reply3</t>
         </is>
@@ -3518,8 +2960,9 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" display="https://www.v2ex.com/t/1201439#reply0" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" display="https://www.v2ex.com/t/1200917#reply1" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" display="https://www.v2ex.com/t/1202057#reply0" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" display="https://www.v2ex.com/t/1202059#reply6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" display="https://www.v2ex.com/t/1202024#reply6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3568,7 +3011,7 @@
           <t>字节</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>https://jobs.bytedance.com/referral/pc/position?token=MTsxNzUxNDMyMjkxNDcyOzY3MjM3OTA0NDAwNjEzNzE5MTY7NzQyNTkxMTUwMzAxNjc1NzU0MTsx</t>
         </is>
@@ -3611,7 +3054,7 @@
           <t xml:space="preserve">字节跳动 </t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1147480#reply1</t>
         </is>
